--- a/Pricing Logic/modules/uploads/module_2_1126.xlsx
+++ b/Pricing Logic/modules/uploads/module_2_1126.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="225">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,31 +37,22 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>كوفى ميكس بونجورنو ظرف - 12 جم</t>
-  </si>
-  <si>
-    <t>نسكافيه 3*1 - 18 جم</t>
+    <t>زيت كريستال الممتاز خليط - 1 لتر</t>
   </si>
   <si>
     <t>عسل البوادى اسود - 680 جم</t>
   </si>
   <si>
-    <t>فجيتار كنور عادى - 35 جم</t>
-  </si>
-  <si>
-    <t>كنور مرقة دجاج 12 مكعب عبوة اقتصادية- 108 جم</t>
-  </si>
-  <si>
-    <t>كنور فيجيتار حار - 35 جم</t>
+    <t>لبن بخيره - 1 لتر</t>
   </si>
   <si>
     <t>لبن نيدو اساسى ازرق ظرف - 25 جم</t>
   </si>
   <si>
-    <t>مرقة دجاج كنور فاين فودز شريط - 8 جم</t>
-  </si>
-  <si>
-    <t>كورونا كاكاو محلي  وسط ( 60 جرام )- 25 جنية</t>
+    <t>لبن جهينة مكس فراولة - 200 مل</t>
+  </si>
+  <si>
+    <t>البوادي حلاوة- 255 جم</t>
   </si>
   <si>
     <t>فاين مناديل فلافي جيب- 10 باكت</t>
@@ -70,10 +61,7 @@
     <t>عصير جهينة تفاح - 1 لتر</t>
   </si>
   <si>
-    <t>عصير جهينة كوكتيل - 1 لتر</t>
-  </si>
-  <si>
-    <t>بيبسى - 2.43 لتر</t>
+    <t>كوكا كولا جيب - 240 مل</t>
   </si>
   <si>
     <t>جبنة دومتى فيتا بلس - 125 جم</t>
@@ -88,6 +76,9 @@
     <t>تونة دولفين قطع بارد - 185 جم</t>
   </si>
   <si>
+    <t>لبن المراعى تريتس موز - 200 مل</t>
+  </si>
+  <si>
     <t>حلاوة الرشيدى الميزان سبريد شوكولاتة - 300 جم</t>
   </si>
   <si>
@@ -97,9 +88,6 @@
     <t>%طحينة الرشيدى الميزان خصم 10 - 255 جم</t>
   </si>
   <si>
-    <t>نواعم بسكويت- 5 ج</t>
-  </si>
-  <si>
     <t>المراعي لبن فراولة (وفر جنية) 200 مل</t>
   </si>
   <si>
@@ -112,16 +100,16 @@
     <t>طحينة الرشيدى الميزان - 500 جم</t>
   </si>
   <si>
-    <t>دروو كيك زبده- 12 جنية</t>
-  </si>
-  <si>
-    <t>برسيل جل اوتوماتيك - 2.6 كجم</t>
-  </si>
-  <si>
     <t>هارفست فول مدمس سادة - 400 جم</t>
   </si>
   <si>
-    <t>مناديل فاميليا مطبخ 2 طبقة - 2 رول</t>
+    <t>ريحانة كسبرة مطحونة- 20 جم</t>
+  </si>
+  <si>
+    <t>شويبس جولد خوخ - 300 مل</t>
+  </si>
+  <si>
+    <t>حفاضات مولفيكس مقاس 3 - 80 حفاضة</t>
   </si>
   <si>
     <t>حفاضات مولفيكس ماكسى مقاس 4 - 80 حفاضة</t>
@@ -133,12 +121,12 @@
     <t>حفاضات مولفيكس بانتس جونيور مقاس 5 - 58 حفاضة</t>
   </si>
   <si>
+    <t>صلصة هارفست طماطم صفيح - 800 جم</t>
+  </si>
+  <si>
     <t>اولويز الترا رفيعة طويل جدا 3*1 بالاعشاب - 7 فوطة</t>
   </si>
   <si>
-    <t>ريحانة حمص شام- 500 جم</t>
-  </si>
-  <si>
     <t>حفاضات مولفيكس بانتس مقاس 3 - 58 حفاضة</t>
   </si>
   <si>
@@ -163,19 +151,19 @@
     <t>حفاضات بى بم بانتس جامبو مقاس 4 - 56 حفاضة</t>
   </si>
   <si>
-    <t>كورونا شوكولاتة أكسترا ميلك وسط- 20 جنية</t>
-  </si>
-  <si>
-    <t>تونة دولفين قطع 140 جم + 10 جم - 150 جم</t>
-  </si>
-  <si>
-    <t>صلصة هاينز - 360 جم</t>
-  </si>
-  <si>
-    <t>حفاضات بيبى جوى مضغوطة جيب مانع للتسريب وسط مقاس 3 - 58 حفاضة</t>
-  </si>
-  <si>
-    <t>حفاضات بيبى جوى مضغوطة جيب مانع للتسريب كبير مقاس 4 - 58 حفاضة</t>
+    <t>سبرايت - 2.45 لتر</t>
+  </si>
+  <si>
+    <t>حلاوة الرشيدى الميزان - 130 جم</t>
+  </si>
+  <si>
+    <t>جبنة كيرى بالقشطة - 8 قطعه</t>
+  </si>
+  <si>
+    <t>تونة دولفين مفتتة حار 170 جم + 30 جم - 200 جم</t>
+  </si>
+  <si>
+    <t>حلو الشام كريم شانتيه - 45 جم</t>
   </si>
   <si>
     <t>حفاضات بيبى جوى مضغوطة جيب مانع للتسريب كبير جدا مقاس 5 - 58 حفاضة</t>
@@ -187,27 +175,33 @@
     <t>اوكسى اوتوماتيك نسيم الشرق 4 ك + 1 ك -Delisted 5 كجم</t>
   </si>
   <si>
-    <t>مسحوق غسيل فل يدوى ابيض - 2.5 كجم</t>
-  </si>
-  <si>
     <t>دومتي جو عصير مانجو- 200 مل</t>
   </si>
   <si>
+    <t>عصير سن توب توت مشكل - 250 مل</t>
+  </si>
+  <si>
+    <t>عصير سن توب مانجو الفونسو - 250 مل</t>
+  </si>
+  <si>
+    <t>عصير سن توب فواكه مشكلة - 250 مل</t>
+  </si>
+  <si>
+    <t>عصير سن توب برتقال - 250 مل</t>
+  </si>
+  <si>
+    <t>عصير سن توب اناناس - 250 مل</t>
+  </si>
+  <si>
     <t>رويال أعشاب ينسون - 50 فتلة</t>
   </si>
   <si>
-    <t>رويال أعشاب ليمون جنزبيل - 12 فتلة</t>
-  </si>
-  <si>
     <t>رويال أعشاب ليمون جنزبيل - 20 فتلة</t>
   </si>
   <si>
     <t>رويال أعشاب ليمون جنزبيل - 50 فتلة</t>
   </si>
   <si>
-    <t>حفاضات موليفكس جامبو مقاس 2 - 60 حفاضة</t>
-  </si>
-  <si>
     <t>حفاضات بى بم جامبو بانتس مقاس 6 - 46 حفاضة</t>
   </si>
   <si>
@@ -217,18 +211,9 @@
     <t>مسحوق باهى يدوى لافندر - 1 كجم</t>
   </si>
   <si>
-    <t>دروو  باوند كيك زبدة - 7 جنية</t>
-  </si>
-  <si>
-    <t>سندريلا سميكه طويل - 9 فوطة</t>
-  </si>
-  <si>
     <t>الحاوي أرز مصري - 5 كيلو</t>
   </si>
   <si>
-    <t>مناديل فاميليا مطبخ كلاسيك 6 رول + 2 رول هدية - 8 رول</t>
-  </si>
-  <si>
     <t>دروو كيك باوند زبده - 10 جنية</t>
   </si>
   <si>
@@ -238,19 +223,22 @@
     <t>سوفى ماكسى سميكة طويل جدا بالمسك عرض خاص - 14 فوطة</t>
   </si>
   <si>
-    <t>لبان تشكلتس نعناع - 0.5 جنية</t>
-  </si>
-  <si>
     <t>شويبس ليمون نعناع جيب - 240 مل</t>
   </si>
   <si>
+    <t>شويبس رمان جيب - 240 مل</t>
+  </si>
+  <si>
     <t>شويبس جولد اناناس جيب - 240 مل</t>
   </si>
   <si>
+    <t>جبنة رودس زيتون - 250 جم</t>
+  </si>
+  <si>
     <t>أطعم مرقة دجاج شريط - 8 جم</t>
   </si>
   <si>
-    <t>بسكويت بيمبو بندق - 5 جنية</t>
+    <t>مكرونة خطيرة شعرية - 280 جم</t>
   </si>
   <si>
     <t>مربى الرشيدى الميزان مشمش - 340 جم</t>
@@ -259,6 +247,12 @@
     <t>مربى الرشيدى الميزان مشمش - 700 جم</t>
   </si>
   <si>
+    <t>عسل اسود الرشيدى الميزان بلاستيك - 650 جم</t>
+  </si>
+  <si>
+    <t>سندة زيت خليط - 700 مل</t>
+  </si>
+  <si>
     <t>حفاضات جود كير مقاس 3 - 100 حفاضة</t>
   </si>
   <si>
@@ -268,10 +262,16 @@
     <t>مايونيز هاينز الكبير - 14 جم</t>
   </si>
   <si>
+    <t>اريال يدوي لافندر - 1.5 كجم</t>
+  </si>
+  <si>
+    <t>-اريال اوتوماتيك لافندر - 2.5 كجم</t>
+  </si>
+  <si>
     <t>حلاوة بار الرشيدى الميزان - 21 جم</t>
   </si>
   <si>
-    <t>مكرونة بساطة لسان عصفور - 350 جم</t>
+    <t>كاتشب هاينز اسكويزى دوى باك - 285 جم</t>
   </si>
   <si>
     <t>حفاضات بى بم جامبو مقاس 5 - 58 حفاضة</t>
@@ -283,46 +283,58 @@
     <t>صابون كامى اناقة -- 110 جم</t>
   </si>
   <si>
+    <t>صابون كامى حيوية - 110 جم</t>
+  </si>
+  <si>
     <t>صابون كامى كلاسيك -- 110 جم</t>
   </si>
   <si>
+    <t>صابون كامى رومانسية - 110 جم</t>
+  </si>
+  <si>
     <t>اوكسى نسيم الربيع --Delisted 1.5 كجم</t>
   </si>
   <si>
     <t>اوكسى جل بلاك - 3 كجم</t>
   </si>
   <si>
+    <t>صابون كامى اناقة - 165 جم</t>
+  </si>
+  <si>
+    <t>صابون كامى كلاسيك - 165 جم</t>
+  </si>
+  <si>
+    <t>صابون كامى رومانسية - 165 جم</t>
+  </si>
+  <si>
+    <t>حفاضات بامبرز بانتس مقاس 6 - 48 حفاضة</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 540 مل</t>
+  </si>
+  <si>
+    <t>طحينة البوادى ظرف - 42 جم</t>
+  </si>
+  <si>
     <t>اوكسى جل اوتوماتيك لافندر - 3 كجم</t>
   </si>
   <si>
-    <t>شاى الكبوس ناعم عرض 65 ج - 200 جم</t>
+    <t>لوكس صابون حلم السعادة  - 115 جم</t>
+  </si>
+  <si>
+    <t>سمن كريستال ابيض ظرف - 55 جم</t>
   </si>
   <si>
     <t>حفاضات بى بم جامبو بانتس مقاس 5 - 56 حفاضة</t>
   </si>
   <si>
-    <t>حفاضات بى بم جامبو مقاس 4 - 58 حفاضة</t>
-  </si>
-  <si>
     <t>حفاضات بى بم جامبو مقاس 6 - 48 حفاضة</t>
   </si>
   <si>
     <t>يامى نودلز طعم الشطه الحارة- 70 جم</t>
   </si>
   <si>
-    <t>فاين بيبى حفاضات دبل لوك وسط مقاس 3 - 58 حفاضة</t>
-  </si>
-  <si>
-    <t>فاين بيبى حفاضات دبل لوك كبير مقاس 4 - 58 حفاضة</t>
-  </si>
-  <si>
-    <t>فاين بيبى حفاضات دبل لوك ماكس مقاس 5 - 58 حفاضة</t>
-  </si>
-  <si>
-    <t>مناديل بابيا نايلون 2 طبقة - 500 منديل</t>
-  </si>
-  <si>
-    <t>كاتشب هاينز الكبير - 14 جم</t>
+    <t>33% كريم فيانسيه مغذى للشعر بالزيتون و فيتامين ه - 240 مل</t>
   </si>
   <si>
     <t>بسكويت امور سادة حلو - 5 جنية</t>
@@ -331,22 +343,31 @@
     <t>مناديل زينة تريو عرض خاص - 500 منديل</t>
   </si>
   <si>
-    <t>كنور خلطه البرجر - 30 جم</t>
-  </si>
-  <si>
-    <t>مسحوق ليدر عادى لافندر - 2 كجم</t>
-  </si>
-  <si>
-    <t>كيك دروو باوند  بالزبده الطبيعى - 5 جنية</t>
+    <t>عصير جهينة بيور تفاح - 235 مل</t>
+  </si>
+  <si>
+    <t>اريال يدوى لافندر - 2 كجم</t>
+  </si>
+  <si>
+    <t>مسحوق باهى لافندر اوتوماتيك 8 ك + 1 ك - 9 كجم</t>
   </si>
   <si>
     <t>حلاوة بار رويال تيست  - 50 جم</t>
   </si>
   <si>
+    <t>حلو الشام دقيق - 900 جم</t>
+  </si>
+  <si>
+    <t>هارفست فول مصفى بالطحينة خصم %15 - 400 جم</t>
+  </si>
+  <si>
     <t>حفاضات بى بم ميجا مقاس 3 - 80 حفاضة</t>
   </si>
   <si>
-    <t>جبنة لا فاش كيرى شيدر - 8 مثلث</t>
+    <t>جبنة لا فاش كيرى شيدر - 16 مثلث</t>
+  </si>
+  <si>
+    <t>حفاضات بى بم ميجا مقاس 4 - 80 حفاضة</t>
   </si>
   <si>
     <t>حفاضات بى بم ميجا مقاس 5 - 76 حفاضة</t>
@@ -358,21 +379,21 @@
     <t>دروو كيك زبدة (6 قطعة) - 8 جنية</t>
   </si>
   <si>
-    <t>حفاضات بيبى جوى كلوت مضغوطة جامبو مقاس 4 - 58 حفاضة</t>
-  </si>
-  <si>
-    <t>حفاضات بيبى جوى كلوت مضغوط جامبو مقاس 5 - 52 حفاضة</t>
-  </si>
-  <si>
-    <t>حفاضات بيبى جوى كلوت مضغوط جامبو مقاس 6 - 46 حفاضة</t>
-  </si>
-  <si>
     <t>بن العمده محوج غامق - 100 جم</t>
   </si>
   <si>
     <t>بن العمده ساده وسط - 200 جم</t>
   </si>
   <si>
+    <t>مسحوق ليدر عادى لافندر - 65 جم</t>
+  </si>
+  <si>
+    <t>اندومى لحم بقرى - 44 كيس - 75 جم</t>
+  </si>
+  <si>
+    <t>اندومى خضار بالزيت عرض 44 كيس - 75 جم</t>
+  </si>
+  <si>
     <t>اندومى فراخ بالكارى عرض 44  كيس - 75 جم</t>
   </si>
   <si>
@@ -385,10 +406,16 @@
     <t>اوكسى يدوى لافندر -Delisted 1 كجم</t>
   </si>
   <si>
+    <t>زيت حبوبة خليط - 2.4 لتر</t>
+  </si>
+  <si>
     <t>مناديل زينة سحب اروما فراولة عرض خاص 3 قطع - 500 منديل</t>
   </si>
   <si>
-    <t>مناديل زينة سحب اروما عود عرض خاص 3 قطع - 500 منديل</t>
+    <t>كوكا كولا تربو زيرو - 300 مل</t>
+  </si>
+  <si>
+    <t>عصير جهينة مكس بيرى - 235 مل</t>
   </si>
   <si>
     <t>بسكويت اولكر بالتمر 4 قطع - 5 جنية</t>
@@ -403,15 +430,18 @@
     <t>شاور جيل سوبر كرنفال زهور الربيع - 2 لتر</t>
   </si>
   <si>
-    <t>سائل اطباق وفير بلس ليمون اصفر - 40 جم</t>
-  </si>
-  <si>
-    <t>شويبس رمان بلاستيك - 250 مل</t>
+    <t>اوكسى يدوى 16كيس - 110 جم</t>
   </si>
   <si>
     <t>صابون لوكس بشرة مثالية - 115 جم</t>
   </si>
   <si>
+    <t>صابون لوكس بشرة نضرة - 115 جم</t>
+  </si>
+  <si>
+    <t>صابون لوكس سحر الاوركيد - 115 جم</t>
+  </si>
+  <si>
     <t>دروو باوند كيك بالكاكاو الطبيعي - 10 جنية</t>
   </si>
   <si>
@@ -424,22 +454,34 @@
     <t>اوكسى يدوى لافندر -Delisted 500 جم</t>
   </si>
   <si>
+    <t>كل يوم عصير جوافة  - 200 مل</t>
+  </si>
+  <si>
     <t>كل يوم عصير كوكتيل - 200 مل</t>
   </si>
   <si>
-    <t>ميرندا برتقال فيز - عرض الصيف 20جنيه 1.47 لتر</t>
+    <t>كل يوم عصير مانجو - 200 مل</t>
+  </si>
+  <si>
+    <t>توينكيز دبل كريم حجم جديد كريمة اكثر- 5 جنية</t>
+  </si>
+  <si>
+    <t>صابون لوكس بشرة نضرة - 165 جم</t>
+  </si>
+  <si>
+    <t>صابون لوكس سحر الاوركيد - 165 جم</t>
   </si>
   <si>
     <t>صابون لوكس بشرة مثالية - 165 جم</t>
   </si>
   <si>
-    <t>مورو شوكولاتة عادي خصم 10 ج 40 جم</t>
-  </si>
-  <si>
     <t>لبنيتا جبنة مثلثات - 24 مثلث</t>
   </si>
   <si>
-    <t>سندة دقيق - 1 كجم</t>
+    <t>مناديل بابيا مطبخ 3 طبقة 5 رول + 1 رول هدية 6 رول</t>
+  </si>
+  <si>
+    <t>اوكسي يدوي - 175 جم</t>
   </si>
   <si>
     <t>تيكا مارشملو بايت ضفيرة - 3 جرام 1 جنية</t>
@@ -454,9 +496,6 @@
     <t>زيووو شرائح كيرليى ليمون حلو - 5 جنية</t>
   </si>
   <si>
-    <t>زيووو اراميش بافس فلفل حلو - 5 جنية</t>
-  </si>
-  <si>
     <t>حلو الشام ايزى كوك مرقة الدجاج - 6 جم</t>
   </si>
   <si>
@@ -466,61 +505,37 @@
     <t>فرسكا شوكو ستكس شوكولاتة مغطي شوكولاته بيضاءمحشو كاكاو وبندق 2 قطعه</t>
   </si>
   <si>
+    <t>فرسكا ستكس ويفر ملفوف محشو بكريمه الكاكاو والبندق 3 قطعه</t>
+  </si>
+  <si>
     <t>فرسكا شوكو بار شكولاته بيضاء حجم اكبر 5 جنية</t>
   </si>
   <si>
     <t>فرسكا شوكو بار حلاوة12 قطعه حجم اكبر 5 جنية</t>
   </si>
   <si>
-    <t>برسيل يدوى لافندر - 50 جم</t>
-  </si>
-  <si>
-    <t>اريال يدوى لافندر جل- 730 جم</t>
-  </si>
-  <si>
-    <t>سيجنال مكافح التسوس 15 جنيه + فرشة اسنان هدية 15 مل</t>
-  </si>
-  <si>
-    <t>أولويز ماكسى سميكة ناعمة بلمسة الألوڤيرا طويلة + 2 مجانا - 16 فوطة</t>
-  </si>
-  <si>
-    <t>جبنة ابو الولد كريمى سبريد شيدر 20 جنيه - 100 جم</t>
-  </si>
-  <si>
-    <t>مولبد حماية ضد البكتريا طويل جدا 12 + 2 فوطة مجانا - 14 فوطة</t>
+    <t>AAA توشيبا ازرق 2 حجر ريموت شرنك 2 حجر</t>
+  </si>
+  <si>
+    <t>زيت ثمرات خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>لارش ميلت كيك بصوص الكاكاو ومغطي بالكاكاو - 10 جنية</t>
   </si>
   <si>
     <t>مناديل فاميليا تواليت مضغوط - 2 رول</t>
   </si>
   <si>
-    <t>مناديل فاميليا تواليت مضغوط 10 رول + 2 رول هدية - 12 رول</t>
-  </si>
-  <si>
-    <t>حفاضات فاين بيبى مقاس 3 دبل لوك - 80 حفاضة</t>
-  </si>
-  <si>
-    <t>حفاضات فاين بيبى ماكسى مقاس 4 دبل لوك - 80 حفاضة</t>
-  </si>
-  <si>
-    <t>حفاضات فاين بيبى كبير مقاس 5 دبل لوك - 76 حفاضة</t>
-  </si>
-  <si>
-    <t>فاين فلافي سحب 18 قطعة - 480 منديل 480 منديل</t>
-  </si>
-  <si>
-    <t>فاين مناديل تواليت كمفورت 24 رول20+ 4مجانا 24 رول</t>
-  </si>
-  <si>
-    <t>فاين سمارت مناديل تواليت مضغوط 5+1 رول * 2 طبقة 6 رول</t>
+    <t>مناديل بابيا مطبخ 3 طبقات - 2 رول</t>
+  </si>
+  <si>
+    <t>فاين برستيج عرض خاص 500 منديل  "6 شرينك" * 3 طبقة 500 منديل</t>
   </si>
   <si>
     <t>فاين سوبر تول برو مطبخ +1مجانا 6 رول  *3 طبقة 6 رول</t>
   </si>
   <si>
-    <t>اد - مى (عالطبخه) بالبصل والثوم والفلفل - 375 جم</t>
-  </si>
-  <si>
-    <t>أد - مى صوص اربياتا - 375 جم</t>
+    <t>مكرونة شعرية بساطة - 1 كجم</t>
   </si>
   <si>
     <t>ليندو برو برائحه اللافندر - 200 جرام</t>
@@ -538,106 +553,124 @@
     <t>ريد بول 12 كانز - 250 مل</t>
   </si>
   <si>
-    <t>بيتي عصير مانجو عرض خاص 28ج - 1 لتر</t>
+    <t>بيتي عصير كوكتيل عرض خاص 27ج - 1 لتر</t>
+  </si>
+  <si>
+    <t>بيتي عصير أناناس كوكتيل عرض خاص 27ج - 1 لتر</t>
+  </si>
+  <si>
+    <t>بيتي عصير برتقال عرض خاص 27ج - 1 لتر</t>
   </si>
   <si>
     <t>كاتشب هاينز - 6 جرام</t>
   </si>
   <si>
-    <t>جبنة دومتي بلس بالزيتون - 500 جم</t>
-  </si>
-  <si>
-    <t>دومتي جبنة اسطنبولي بلس - 500 جم</t>
+    <t>-اريال أتوماتيك لافندر 9 كجم - 2 كيس</t>
+  </si>
+  <si>
+    <t>دومتي جبنة فيتا بلس - 250 جم</t>
   </si>
   <si>
     <t>دومتي جبنة فلمنك - 250 جم</t>
   </si>
   <si>
-    <t>دومتي جبنة فلمنك - 500 جم</t>
-  </si>
-  <si>
-    <t>دومتي جبنة فيتا بلس بسطرمة - 250 جم</t>
-  </si>
-  <si>
-    <t>دومتي جبنة فيتا بلس بسطرمة - 500 جم</t>
-  </si>
-  <si>
-    <t>دومتي جبنة فيتا بلس رومي - 500 جم</t>
-  </si>
-  <si>
-    <t>دومتي جبنة فيتا بلس لايت - 250 جم</t>
-  </si>
-  <si>
-    <t>دومتي جبنة فيتا بلس لايت - 500 جم</t>
-  </si>
-  <si>
     <t>المراعي جبنة فيتا بالزيتون - 250 جم</t>
   </si>
   <si>
-    <t>زيووو شرائح بالت خضروات - 65 جم</t>
-  </si>
-  <si>
-    <t>اوكسي يدوي 32 كيس - 50 جم</t>
+    <t>سن توب عصير يوسفي مشطشط - 250 مل</t>
+  </si>
+  <si>
+    <t>اولويز الترا سليم 3*1 طويل -عرض 22+4 مجانا 26 فوطة</t>
+  </si>
+  <si>
+    <t>باراديس طوفي - 240 قطعه</t>
+  </si>
+  <si>
+    <t>باندا مثلثات - 16 قطعه</t>
+  </si>
+  <si>
+    <t>باندا جورمية مثلثات - 16 قطعه</t>
+  </si>
+  <si>
+    <t>باندا جورمية جبنة مربعات ب القشطة - 6 قطعه</t>
+  </si>
+  <si>
+    <t>جبنة باندا فيتا  - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا رومى - 250 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا شيدر - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا رومى - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا شيدر  - 125 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا بسطرمة  - 125 جم</t>
+  </si>
+  <si>
+    <t>جبنة ديرى فيتا بلس - 500 جم</t>
   </si>
   <si>
     <t>فيانسيه شامبو 7فى1 اكياس بالبصل والخروع 5 مل</t>
   </si>
   <si>
-    <t>اوريو بسكوت بكريمة بطعم الشوكولاتة والبندق  - 48 جرام</t>
-  </si>
-  <si>
-    <t>بونكس اوتوماتيك بلمسة الداوني - 9 كجم</t>
+    <t>فيانسيه حمام كريم7فى1 بالأفاوكادو والزيتون 35 مل</t>
+  </si>
+  <si>
+    <t>جبنة باندا فيتا 125 جرام</t>
   </si>
   <si>
     <t>راز كب كيك ذهبي محشو مربي فراولة - 12 قطعه</t>
   </si>
   <si>
-    <t>بريل زجاج 600 جرام  تفاح 600 جم</t>
-  </si>
-  <si>
-    <t>مولفيكس بانتس جامبو اقتصادي مقاس 5 - 56 حفاضة</t>
+    <t>البوادي مربى كريمي فراولة - 365 جرام</t>
   </si>
   <si>
     <t>مولفيكس بانتس ماكسى ضد البكتريا ميجا مقاس 4 - 76 حفاضة</t>
   </si>
   <si>
-    <t>مولفيكس بانتس كبير ضد البكتريا ميجا مقاس 5 - 66 حفاضة</t>
+    <t>مولفيكس بانتس كبير جدا ضد البكتريا ميجا مقاس 6 - 60 حفاضة</t>
   </si>
   <si>
     <t>موني سوبر سترتش كبير مقاس 5 - 80 حفاضة</t>
   </si>
   <si>
+    <t>بيج كولا ليمون - 360 مل</t>
+  </si>
+  <si>
+    <t>مولفيكس بانتس  مقاس 6 كبير جدا 46 حفاضة</t>
+  </si>
+  <si>
     <t>بسكويت بيمبو فيجان لارج - 12 قطعه</t>
   </si>
   <si>
+    <t>لبان ترايدنت ميكس توت حجم اكبر لبان اكتر- 7 قطعه</t>
+  </si>
+  <si>
     <t>الشمعدان ميني تيبو جوز هند - 6 قطعه</t>
   </si>
   <si>
     <t>الشمعدان امور بسكويت سادة حلو - 6 قطعه</t>
   </si>
   <si>
-    <t>الشمعدان هيرو ساندويتش بسكويت محشو بكريمة الكاكاو- 12 قطعه</t>
-  </si>
-  <si>
-    <t>بسكويت ويفر محشو بكريمة البندق HD الشمعدان - 6 قطعه</t>
+    <t>الرشيدي الميزان حلاوة - 960 جم</t>
   </si>
   <si>
     <t>الرشيدي الميزان حلاوة سبريد - 300 جم</t>
   </si>
   <si>
-    <t>ماكسى كانز ليمون اورجينال - 300 مل</t>
-  </si>
-  <si>
-    <t>حفاضات بى بم بانتس مقاس 4 - 76 حفاضة</t>
+    <t>ماكسى كانز برتقال اورجينال - 300 مل</t>
   </si>
   <si>
     <t>حفاضات بى بم بانتس مقاس 5 - 72 حفاضة</t>
   </si>
   <si>
-    <t>اندومى سوبر مى خضار - 5 جنيه - 56 جم</t>
-  </si>
-  <si>
-    <t>اندومى لحمة بيف  -5جنيه - 56 جم</t>
+    <t>اريال اوتوماتيك برائحة البخور 2 كيس-- 9 كجم</t>
   </si>
   <si>
     <t>ماكسي كـولا - 2 لتر</t>
@@ -646,16 +679,10 @@
     <t>ماكسـي ليمون نعناع - 2 لتر</t>
   </si>
   <si>
-    <t>بيبسي هضبه - 250 مل</t>
-  </si>
-  <si>
-    <t>أولويز ماكسى سميكة ناعمة بلمسة الألوڤيرا طويلة جدا + 4 مجانا- 24 فوطة</t>
-  </si>
-  <si>
-    <t>أولويز ماكسى سميكة ناعمة حساس الألوڤيرا طويلة جدا + 6 مجانا- 26 فوطة</t>
-  </si>
-  <si>
-    <t>أولويز ماكسى سميكة ناعمةحساس بلمسة الألوڤيرا طويلة + 6  فوط مجانا- 28 فوطة</t>
+    <t>ماكسي بـرتقال - 2 لتر</t>
+  </si>
+  <si>
+    <t>شوكولاتة ديرى ميلك بابلي اوريو - 27 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -1019,7 +1046,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G340"/>
+  <dimension ref="A1:G341"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1047,7 +1074,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -1056,32 +1083,32 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>1680</v>
+        <v>840</v>
       </c>
       <c r="E2" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D3">
-        <v>70</v>
+        <v>43.5</v>
       </c>
       <c r="E3" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
@@ -1090,423 +1117,423 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>1620</v>
+        <v>522</v>
       </c>
       <c r="E4" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D5">
-        <v>135</v>
+        <v>261</v>
       </c>
       <c r="E5" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>70</v>
+        <v>151</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>43.5</v>
+        <v>445</v>
       </c>
       <c r="E6" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D7">
-        <v>261</v>
+        <v>241.75</v>
       </c>
       <c r="E7" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>522</v>
+        <v>967</v>
       </c>
       <c r="E8" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>105</v>
+        <v>206</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>664.5</v>
+        <v>273.25</v>
       </c>
       <c r="E9" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>105</v>
+        <v>214</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>110.75</v>
+        <v>1062</v>
       </c>
       <c r="E10" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>110</v>
+        <v>214</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11">
-        <v>1080</v>
+        <v>44.25</v>
       </c>
       <c r="E11" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>110</v>
+        <v>308</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>135</v>
+        <v>174.75</v>
       </c>
       <c r="E12" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>114</v>
+        <v>413</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13">
-        <v>682.5</v>
+        <v>345</v>
       </c>
       <c r="E13" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>114</v>
+        <v>615</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14">
-        <v>113.75</v>
+        <v>308.75</v>
       </c>
       <c r="E14" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>152</v>
+        <v>903</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15">
-        <v>967</v>
+        <v>382.75</v>
       </c>
       <c r="E15" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>152</v>
+        <v>936</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C16">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>241.75</v>
+        <v>609</v>
       </c>
       <c r="E16" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>159</v>
+        <v>936</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C17">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D17">
-        <v>373.5</v>
+        <v>50.75</v>
       </c>
       <c r="E17" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>159</v>
+        <v>942</v>
       </c>
       <c r="B18" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18">
-        <v>747</v>
+        <v>609</v>
       </c>
       <c r="E18" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>159</v>
+        <v>942</v>
       </c>
       <c r="B19" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C19">
         <v>3</v>
       </c>
       <c r="D19">
-        <v>41.5</v>
+        <v>101.5</v>
       </c>
       <c r="E19" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>192</v>
+        <v>944</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C20">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D20">
-        <v>20.5</v>
+        <v>55</v>
       </c>
       <c r="E20" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>192</v>
+        <v>944</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D21">
-        <v>984</v>
+        <v>1320</v>
       </c>
       <c r="E21" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>308</v>
+        <v>944</v>
       </c>
       <c r="B22" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22">
-        <v>180</v>
+        <v>2640</v>
       </c>
       <c r="E22" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>413</v>
+        <v>944</v>
       </c>
       <c r="B23" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D23">
-        <v>345</v>
+        <v>660</v>
       </c>
       <c r="E23" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>415</v>
+        <v>958</v>
       </c>
       <c r="B24" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24">
-        <v>345</v>
+        <v>275.25</v>
       </c>
       <c r="E24" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>589</v>
+        <v>962</v>
       </c>
       <c r="B25" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>216.75</v>
+        <v>675</v>
       </c>
       <c r="E25" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>903</v>
+        <v>962</v>
       </c>
       <c r="B26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D26">
-        <v>388</v>
+        <v>56.25</v>
       </c>
       <c r="E26" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>936</v>
+        <v>964</v>
       </c>
       <c r="B27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D27">
-        <v>609</v>
+        <v>26.25</v>
       </c>
       <c r="E27" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>936</v>
+        <v>964</v>
       </c>
       <c r="B28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C28">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D28">
-        <v>50.75</v>
+        <v>262.5</v>
       </c>
       <c r="E28" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>942</v>
+        <v>964</v>
       </c>
       <c r="B29" t="s">
         <v>22</v>
@@ -1515,2687 +1542,2687 @@
         <v>1</v>
       </c>
       <c r="D29">
-        <v>609</v>
+        <v>1050</v>
       </c>
       <c r="E29" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>942</v>
+        <v>964</v>
       </c>
       <c r="B30" t="s">
         <v>22</v>
       </c>
       <c r="C30">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D30">
-        <v>101.5</v>
+        <v>525</v>
       </c>
       <c r="E30" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>944</v>
+        <v>965</v>
       </c>
       <c r="B31" t="s">
         <v>23</v>
       </c>
       <c r="C31">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D31">
-        <v>669</v>
+        <v>1194</v>
       </c>
       <c r="E31" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>944</v>
+        <v>965</v>
       </c>
       <c r="B32" t="s">
         <v>23</v>
       </c>
       <c r="C32">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D32">
-        <v>1338</v>
+        <v>49.75</v>
       </c>
       <c r="E32" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>944</v>
+        <v>999</v>
       </c>
       <c r="B33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33">
-        <v>2676</v>
+        <v>266.75</v>
       </c>
       <c r="E33" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>944</v>
+        <v>1049</v>
       </c>
       <c r="B34" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C34">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D34">
-        <v>55.75</v>
+        <v>284.75</v>
       </c>
       <c r="E34" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>962</v>
+        <v>1050</v>
       </c>
       <c r="B35" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C35">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D35">
-        <v>56.25</v>
+        <v>288.25</v>
       </c>
       <c r="E35" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>962</v>
+        <v>1054</v>
       </c>
       <c r="B36" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36">
-        <v>675</v>
+        <v>1164</v>
       </c>
       <c r="E36" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>964</v>
+        <v>1054</v>
       </c>
       <c r="B37" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C37">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D37">
-        <v>262.5</v>
+        <v>97</v>
       </c>
       <c r="E37" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>964</v>
+        <v>1339</v>
       </c>
       <c r="B38" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C38">
         <v>1</v>
       </c>
       <c r="D38">
-        <v>1050</v>
+        <v>4152</v>
       </c>
       <c r="E38" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>964</v>
+        <v>1339</v>
       </c>
       <c r="B39" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C39">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D39">
-        <v>26.25</v>
+        <v>173</v>
       </c>
       <c r="E39" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>964</v>
+        <v>1457</v>
       </c>
       <c r="B40" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C40">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D40">
-        <v>525</v>
+        <v>118.5</v>
       </c>
       <c r="E40" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>965</v>
+        <v>1655</v>
       </c>
       <c r="B41" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C41">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D41">
-        <v>49.75</v>
+        <v>335</v>
       </c>
       <c r="E41" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>965</v>
+        <v>1705</v>
       </c>
       <c r="B42" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D42">
-        <v>1194</v>
+        <v>416</v>
       </c>
       <c r="E42" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>972</v>
+        <v>1705</v>
       </c>
       <c r="B43" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43">
-        <v>303</v>
+        <v>832</v>
       </c>
       <c r="E43" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44">
-        <v>972</v>
+        <v>1706</v>
       </c>
       <c r="B44" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D44">
-        <v>50.5</v>
+        <v>815</v>
       </c>
       <c r="E44" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45">
-        <v>999</v>
+        <v>1706</v>
       </c>
       <c r="B45" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C45">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D45">
-        <v>266.75</v>
+        <v>407.5</v>
       </c>
       <c r="E45" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46">
-        <v>1049</v>
+        <v>1722</v>
       </c>
       <c r="B46" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46">
-        <v>284.75</v>
+        <v>511</v>
       </c>
       <c r="E46" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47">
-        <v>1050</v>
+        <v>1722</v>
       </c>
       <c r="B47" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C47">
         <v>2</v>
       </c>
       <c r="D47">
-        <v>288.25</v>
+        <v>127.75</v>
       </c>
       <c r="E47" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48">
-        <v>1054</v>
+        <v>2100</v>
       </c>
       <c r="B48" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C48">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D48">
-        <v>97</v>
+        <v>995.25</v>
       </c>
       <c r="E48" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49">
-        <v>1054</v>
+        <v>2100</v>
       </c>
       <c r="B49" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C49">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D49">
-        <v>1164</v>
+        <v>331.75</v>
       </c>
       <c r="E49" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50">
-        <v>1120</v>
+        <v>2109</v>
       </c>
       <c r="B50" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D50">
-        <v>269.5</v>
+        <v>63.25</v>
       </c>
       <c r="E50" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51">
-        <v>1120</v>
+        <v>2109</v>
       </c>
       <c r="B51" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D51">
-        <v>38.5</v>
+        <v>759</v>
       </c>
       <c r="E51" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52">
-        <v>1294</v>
+        <v>2213</v>
       </c>
       <c r="B52" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D52">
-        <v>708</v>
+        <v>272</v>
       </c>
       <c r="E52" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53">
-        <v>1339</v>
+        <v>2213</v>
       </c>
       <c r="B53" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D53">
-        <v>4140</v>
+        <v>136</v>
       </c>
       <c r="E53" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54">
-        <v>1339</v>
+        <v>2213</v>
       </c>
       <c r="B54" t="s">
+        <v>36</v>
+      </c>
+      <c r="C54">
+        <v>10</v>
+      </c>
+      <c r="D54">
         <v>34</v>
       </c>
-      <c r="C54">
-        <v>3</v>
-      </c>
-      <c r="D54">
-        <v>172.5</v>
-      </c>
       <c r="E54" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55">
-        <v>1701</v>
+        <v>2213</v>
       </c>
       <c r="B55" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55">
-        <v>175.25</v>
+        <v>544</v>
       </c>
       <c r="E55" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56">
-        <v>1706</v>
+        <v>2362</v>
       </c>
       <c r="B56" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C56">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D56">
-        <v>407.5</v>
+        <v>924</v>
       </c>
       <c r="E56" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57">
-        <v>1706</v>
+        <v>2362</v>
       </c>
       <c r="B57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C57">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D57">
-        <v>815</v>
+        <v>308</v>
       </c>
       <c r="E57" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58">
-        <v>1722</v>
+        <v>2364</v>
       </c>
       <c r="B58" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D58">
-        <v>127.75</v>
+        <v>1167</v>
       </c>
       <c r="E58" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59">
-        <v>1722</v>
+        <v>2364</v>
       </c>
       <c r="B59" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D59">
-        <v>511</v>
+        <v>97.25</v>
       </c>
       <c r="E59" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60">
-        <v>2100</v>
+        <v>2366</v>
       </c>
       <c r="B60" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C60">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D60">
-        <v>331.75</v>
+        <v>1167</v>
       </c>
       <c r="E60" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61">
-        <v>2100</v>
+        <v>2366</v>
       </c>
       <c r="B61" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D61">
-        <v>995.25</v>
+        <v>97.25</v>
       </c>
       <c r="E61" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62">
-        <v>2213</v>
+        <v>2376</v>
       </c>
       <c r="B62" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D62">
-        <v>548</v>
+        <v>103.5</v>
       </c>
       <c r="E62" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63">
-        <v>2213</v>
+        <v>2376</v>
       </c>
       <c r="B63" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C63">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D63">
-        <v>137</v>
+        <v>4968</v>
       </c>
       <c r="E63" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64">
-        <v>2213</v>
+        <v>2376</v>
       </c>
       <c r="B64" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C64">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D64">
-        <v>274</v>
+        <v>1242</v>
       </c>
       <c r="E64" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65">
-        <v>2213</v>
+        <v>2402</v>
       </c>
       <c r="B65" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C65">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D65">
-        <v>34.25</v>
+        <v>100.5</v>
       </c>
       <c r="E65" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66">
-        <v>2271</v>
+        <v>2402</v>
       </c>
       <c r="B66" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C66">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D66">
-        <v>75.75</v>
+        <v>603</v>
       </c>
       <c r="E66" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67">
-        <v>2271</v>
+        <v>2417</v>
       </c>
       <c r="B67" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C67">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D67">
-        <v>1515</v>
+        <v>222.75</v>
       </c>
       <c r="E67" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68">
-        <v>2362</v>
+        <v>2417</v>
       </c>
       <c r="B68" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C68">
         <v>29</v>
       </c>
       <c r="D68">
-        <v>924</v>
+        <v>668.25</v>
       </c>
       <c r="E68" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69">
-        <v>2362</v>
+        <v>2418</v>
       </c>
       <c r="B69" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C69">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="D69">
-        <v>308</v>
+        <v>274.25</v>
       </c>
       <c r="E69" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70">
-        <v>2364</v>
+        <v>2418</v>
       </c>
       <c r="B70" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C70">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D70">
-        <v>1212</v>
+        <v>822.75</v>
       </c>
       <c r="E70" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71">
-        <v>2364</v>
+        <v>2419</v>
       </c>
       <c r="B71" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C71">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="D71">
-        <v>101</v>
+        <v>274.25</v>
       </c>
       <c r="E71" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72">
-        <v>2366</v>
+        <v>2419</v>
       </c>
       <c r="B72" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C72">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D72">
-        <v>100</v>
+        <v>822.75</v>
       </c>
       <c r="E72" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73">
-        <v>2366</v>
+        <v>2775</v>
       </c>
       <c r="B73" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D73">
-        <v>1200</v>
+        <v>226.25</v>
       </c>
       <c r="E73" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74">
-        <v>2376</v>
+        <v>2821</v>
       </c>
       <c r="B74" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D74">
-        <v>1242</v>
+        <v>534</v>
       </c>
       <c r="E74" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75">
-        <v>2376</v>
+        <v>2821</v>
       </c>
       <c r="B75" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D75">
-        <v>4968</v>
+        <v>22.25</v>
       </c>
       <c r="E75" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76">
-        <v>2376</v>
+        <v>2836</v>
       </c>
       <c r="B76" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C76">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D76">
-        <v>103.5</v>
+        <v>80.25</v>
       </c>
       <c r="E76" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77">
-        <v>2402</v>
+        <v>2836</v>
       </c>
       <c r="B77" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C77">
-        <v>1</v>
+        <v>138</v>
       </c>
       <c r="D77">
-        <v>603</v>
+        <v>802.5</v>
       </c>
       <c r="E77" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78">
-        <v>2402</v>
+        <v>2836</v>
       </c>
       <c r="B78" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D78">
-        <v>100.5</v>
+        <v>4815</v>
       </c>
       <c r="E78" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79">
-        <v>2417</v>
+        <v>2859</v>
       </c>
       <c r="B79" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C79">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D79">
-        <v>668.25</v>
+        <v>1644</v>
       </c>
       <c r="E79" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80">
-        <v>2417</v>
+        <v>2859</v>
       </c>
       <c r="B80" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C80">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="D80">
-        <v>222.75</v>
+        <v>411</v>
       </c>
       <c r="E80" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81">
-        <v>2418</v>
+        <v>2859</v>
       </c>
       <c r="B81" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C81">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="D81">
-        <v>274.25</v>
+        <v>34.25</v>
       </c>
       <c r="E81" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82">
-        <v>2418</v>
+        <v>2859</v>
       </c>
       <c r="B82" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C82">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D82">
-        <v>822.75</v>
+        <v>822</v>
       </c>
       <c r="E82" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83">
-        <v>2419</v>
+        <v>3028</v>
       </c>
       <c r="B83" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C83">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D83">
-        <v>822.75</v>
+        <v>1063.5</v>
       </c>
       <c r="E83" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84">
-        <v>2419</v>
+        <v>3028</v>
       </c>
       <c r="B84" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C84">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="D84">
-        <v>274.25</v>
+        <v>177.25</v>
       </c>
       <c r="E84" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85">
-        <v>3072</v>
+        <v>3577</v>
       </c>
       <c r="B85" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C85">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D85">
-        <v>193</v>
+        <v>341.5</v>
       </c>
       <c r="E85" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86">
-        <v>3072</v>
+        <v>3577</v>
       </c>
       <c r="B86" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C86">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D86">
-        <v>2316</v>
+        <v>1024.5</v>
       </c>
       <c r="E86" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87">
-        <v>3429</v>
+        <v>3615</v>
       </c>
       <c r="B87" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C87">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D87">
-        <v>1080</v>
+        <v>194.5</v>
       </c>
       <c r="E87" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88">
-        <v>3429</v>
+        <v>3615</v>
       </c>
       <c r="B88" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C88">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D88">
-        <v>45</v>
+        <v>4668</v>
       </c>
       <c r="E88" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89">
-        <v>3429</v>
+        <v>3615</v>
       </c>
       <c r="B89" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D89">
-        <v>2160</v>
+        <v>1167</v>
       </c>
       <c r="E89" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90">
-        <v>3429</v>
+        <v>3658</v>
       </c>
       <c r="B90" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C90">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D90">
-        <v>540</v>
+        <v>866.25</v>
       </c>
       <c r="E90" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91">
-        <v>3478</v>
+        <v>3847</v>
       </c>
       <c r="B91" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C91">
         <v>2</v>
       </c>
       <c r="D91">
-        <v>385</v>
+        <v>99.25</v>
       </c>
       <c r="E91" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92">
-        <v>3575</v>
+        <v>3889</v>
       </c>
       <c r="B92" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C92">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D92">
-        <v>888.75</v>
+        <v>248.25</v>
       </c>
       <c r="E92" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93">
-        <v>3575</v>
+        <v>3891</v>
       </c>
       <c r="B93" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C93">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D93">
-        <v>296.25</v>
+        <v>245.25</v>
       </c>
       <c r="E93" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94">
-        <v>3576</v>
+        <v>3892</v>
       </c>
       <c r="B94" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C94">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D94">
-        <v>296.25</v>
+        <v>243</v>
       </c>
       <c r="E94" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95">
-        <v>3576</v>
+        <v>3893</v>
       </c>
       <c r="B95" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C95">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D95">
-        <v>888.75</v>
+        <v>252</v>
       </c>
       <c r="E95" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96">
-        <v>3577</v>
+        <v>3894</v>
       </c>
       <c r="B96" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C96">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D96">
-        <v>1024.5</v>
+        <v>248.25</v>
       </c>
       <c r="E96" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97">
-        <v>3577</v>
+        <v>3982</v>
       </c>
       <c r="B97" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C97">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D97">
-        <v>341.5</v>
+        <v>37.5</v>
       </c>
       <c r="E97" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98">
-        <v>3615</v>
+        <v>3982</v>
       </c>
       <c r="B98" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C98">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D98">
-        <v>194.5</v>
+        <v>1350</v>
       </c>
       <c r="E98" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99">
-        <v>3615</v>
+        <v>3984</v>
       </c>
       <c r="B99" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C99">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D99">
-        <v>4668</v>
+        <v>18.25</v>
       </c>
       <c r="E99" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100">
-        <v>3615</v>
+        <v>3984</v>
       </c>
       <c r="B100" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D100">
-        <v>1167</v>
+        <v>1314</v>
       </c>
       <c r="E100" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101">
-        <v>3658</v>
+        <v>3985</v>
       </c>
       <c r="B101" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C101">
         <v>1</v>
       </c>
       <c r="D101">
-        <v>866.25</v>
+        <v>1350</v>
       </c>
       <c r="E101" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102">
-        <v>3664</v>
+        <v>3985</v>
       </c>
       <c r="B102" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C102">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D102">
-        <v>51.75</v>
+        <v>37.5</v>
       </c>
       <c r="E102" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103">
-        <v>3847</v>
+        <v>4043</v>
       </c>
       <c r="B103" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C103">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D103">
-        <v>99.25</v>
+        <v>816.75</v>
       </c>
       <c r="E103" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104">
-        <v>3982</v>
+        <v>4043</v>
       </c>
       <c r="B104" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C104">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D104">
-        <v>37.5</v>
+        <v>272.25</v>
       </c>
       <c r="E104" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105">
-        <v>3982</v>
+        <v>4063</v>
       </c>
       <c r="B105" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C105">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D105">
-        <v>1350</v>
+        <v>55.25</v>
       </c>
       <c r="E105" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106">
-        <v>3983</v>
+        <v>4063</v>
       </c>
       <c r="B106" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C106">
         <v>1</v>
       </c>
       <c r="D106">
-        <v>1428</v>
+        <v>1768</v>
       </c>
       <c r="E106" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107">
-        <v>3983</v>
+        <v>4253</v>
       </c>
       <c r="B107" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C107">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D107">
-        <v>59.5</v>
+        <v>169</v>
       </c>
       <c r="E107" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108">
-        <v>3984</v>
+        <v>4599</v>
       </c>
       <c r="B108" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D108">
-        <v>1314</v>
+        <v>637.5</v>
       </c>
       <c r="E108" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109">
-        <v>3984</v>
+        <v>4599</v>
       </c>
       <c r="B109" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C109">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D109">
-        <v>18.25</v>
+        <v>127.5</v>
       </c>
       <c r="E109" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110">
-        <v>3985</v>
+        <v>5005</v>
       </c>
       <c r="B110" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C110">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D110">
-        <v>37.5</v>
+        <v>222.25</v>
       </c>
       <c r="E110" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111">
-        <v>3985</v>
+        <v>5005</v>
       </c>
       <c r="B111" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C111">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D111">
-        <v>1350</v>
+        <v>31.75</v>
       </c>
       <c r="E111" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112">
-        <v>4030</v>
+        <v>5110</v>
       </c>
       <c r="B112" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C112">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D112">
-        <v>775.5</v>
+        <v>675.75</v>
       </c>
       <c r="E112" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113">
-        <v>4030</v>
+        <v>5165</v>
       </c>
       <c r="B113" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C113">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D113">
-        <v>258.5</v>
+        <v>616</v>
       </c>
       <c r="E113" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114">
-        <v>4043</v>
+        <v>5165</v>
       </c>
       <c r="B114" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C114">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D114">
-        <v>816.75</v>
+        <v>77</v>
       </c>
       <c r="E114" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115">
-        <v>4043</v>
+        <v>5490</v>
       </c>
       <c r="B115" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C115">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D115">
-        <v>272.25</v>
+        <v>290</v>
       </c>
       <c r="E115" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116">
-        <v>4063</v>
+        <v>5491</v>
       </c>
       <c r="B116" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C116">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D116">
-        <v>1784</v>
+        <v>301.75</v>
       </c>
       <c r="E116" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117">
-        <v>4063</v>
+        <v>5493</v>
       </c>
       <c r="B117" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C117">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D117">
-        <v>55.75</v>
+        <v>295</v>
       </c>
       <c r="E117" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118">
-        <v>4253</v>
+        <v>5722</v>
       </c>
       <c r="B118" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C118">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D118">
-        <v>172.5</v>
+        <v>569.25</v>
       </c>
       <c r="E118" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119">
-        <v>4329</v>
+        <v>5769</v>
       </c>
       <c r="B119" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C119">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D119">
-        <v>34</v>
+        <v>495</v>
       </c>
       <c r="E119" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120">
-        <v>4329</v>
+        <v>5769</v>
       </c>
       <c r="B120" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C120">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D120">
-        <v>340</v>
+        <v>27.5</v>
       </c>
       <c r="E120" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121">
-        <v>4586</v>
+        <v>5869</v>
       </c>
       <c r="B121" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C121">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D121">
-        <v>20.5</v>
+        <v>137</v>
       </c>
       <c r="E121" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122">
-        <v>4586</v>
+        <v>6356</v>
       </c>
       <c r="B122" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D122">
-        <v>820</v>
+        <v>306.25</v>
       </c>
       <c r="E122" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123">
-        <v>4599</v>
+        <v>6357</v>
       </c>
       <c r="B123" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C123">
         <v>2</v>
       </c>
       <c r="D123">
-        <v>637.5</v>
+        <v>593</v>
       </c>
       <c r="E123" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124">
-        <v>4599</v>
+        <v>6360</v>
       </c>
       <c r="B124" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C124">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D124">
-        <v>127.5</v>
+        <v>489</v>
       </c>
       <c r="E124" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125">
-        <v>4940</v>
+        <v>6360</v>
       </c>
       <c r="B125" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C125">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D125">
-        <v>242</v>
+        <v>40.75</v>
       </c>
       <c r="E125" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126">
-        <v>5005</v>
+        <v>6494</v>
       </c>
       <c r="B126" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C126">
         <v>1</v>
       </c>
       <c r="D126">
-        <v>222.25</v>
+        <v>586.25</v>
       </c>
       <c r="E126" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127">
-        <v>5005</v>
+        <v>6540</v>
       </c>
       <c r="B127" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C127">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D127">
-        <v>31.75</v>
+        <v>375.5</v>
       </c>
       <c r="E127" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128">
-        <v>5110</v>
+        <v>6540</v>
       </c>
       <c r="B128" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C128">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D128">
-        <v>675.75</v>
+        <v>751</v>
       </c>
       <c r="E128" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129">
-        <v>5165</v>
+        <v>6946</v>
       </c>
       <c r="B129" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C129">
         <v>1</v>
       </c>
       <c r="D129">
-        <v>616</v>
+        <v>509</v>
       </c>
       <c r="E129" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130">
-        <v>5165</v>
+        <v>7084</v>
       </c>
       <c r="B130" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C130">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D130">
-        <v>77</v>
+        <v>228</v>
       </c>
       <c r="E130" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131">
-        <v>5208</v>
+        <v>7084</v>
       </c>
       <c r="B131" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C131">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D131">
-        <v>51.75</v>
+        <v>1368</v>
       </c>
       <c r="E131" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132">
-        <v>5208</v>
+        <v>7191</v>
       </c>
       <c r="B132" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C132">
         <v>1</v>
       </c>
       <c r="D132">
-        <v>1552.5</v>
+        <v>342.25</v>
       </c>
       <c r="E132" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133">
-        <v>5490</v>
+        <v>7202</v>
       </c>
       <c r="B133" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C133">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D133">
-        <v>285.75</v>
+        <v>753.75</v>
       </c>
       <c r="E133" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134">
-        <v>5493</v>
+        <v>7250</v>
       </c>
       <c r="B134" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C134">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D134">
-        <v>294.5</v>
+        <v>313.5</v>
       </c>
       <c r="E134" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135">
-        <v>5769</v>
+        <v>7250</v>
       </c>
       <c r="B135" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C135">
         <v>3</v>
       </c>
       <c r="D135">
-        <v>27.5</v>
+        <v>52.25</v>
       </c>
       <c r="E135" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136">
-        <v>5769</v>
+        <v>7567</v>
       </c>
       <c r="B136" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C136">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D136">
-        <v>495</v>
+        <v>428.5</v>
       </c>
       <c r="E136" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137">
-        <v>5811</v>
+        <v>8157</v>
       </c>
       <c r="B137" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C137">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="D137">
-        <v>579</v>
+        <v>315.5</v>
       </c>
       <c r="E137" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138">
-        <v>5811</v>
+        <v>8157</v>
       </c>
       <c r="B138" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C138">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D138">
-        <v>48.25</v>
+        <v>946.5</v>
       </c>
       <c r="E138" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139">
-        <v>6356</v>
+        <v>8234</v>
       </c>
       <c r="B139" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C139">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D139">
-        <v>306.25</v>
+        <v>195.5</v>
       </c>
       <c r="E139" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140">
-        <v>6357</v>
+        <v>8283</v>
       </c>
       <c r="B140" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C140">
         <v>2</v>
       </c>
       <c r="D140">
-        <v>593</v>
+        <v>58</v>
       </c>
       <c r="E140" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141">
-        <v>6540</v>
+        <v>8283</v>
       </c>
       <c r="B141" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C141">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D141">
-        <v>375.5</v>
+        <v>696</v>
       </c>
       <c r="E141" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142">
-        <v>6540</v>
+        <v>8284</v>
       </c>
       <c r="B142" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C142">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D142">
-        <v>751</v>
+        <v>58</v>
       </c>
       <c r="E142" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143">
-        <v>6946</v>
+        <v>8284</v>
       </c>
       <c r="B143" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C143">
         <v>1</v>
       </c>
       <c r="D143">
-        <v>509</v>
+        <v>696</v>
       </c>
       <c r="E143" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144">
-        <v>7084</v>
+        <v>8285</v>
       </c>
       <c r="B144" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C144">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D144">
-        <v>228</v>
+        <v>696</v>
       </c>
       <c r="E144" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145">
-        <v>7084</v>
+        <v>8285</v>
       </c>
       <c r="B145" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C145">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D145">
-        <v>1368</v>
+        <v>58</v>
       </c>
       <c r="E145" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146">
-        <v>7250</v>
+        <v>8286</v>
       </c>
       <c r="B146" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C146">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D146">
-        <v>52.25</v>
+        <v>58</v>
       </c>
       <c r="E146" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147">
-        <v>7250</v>
+        <v>8286</v>
       </c>
       <c r="B147" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C147">
         <v>1</v>
       </c>
       <c r="D147">
-        <v>313.5</v>
+        <v>696</v>
       </c>
       <c r="E147" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148">
-        <v>7706</v>
+        <v>8355</v>
       </c>
       <c r="B148" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C148">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D148">
-        <v>165</v>
+        <v>326.75</v>
       </c>
       <c r="E148" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149">
-        <v>8157</v>
+        <v>8660</v>
       </c>
       <c r="B149" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C149">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D149">
-        <v>946.5</v>
+        <v>756.5</v>
       </c>
       <c r="E149" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150">
-        <v>8157</v>
+        <v>8753</v>
       </c>
       <c r="B150" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C150">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="D150">
-        <v>315.5</v>
+        <v>969</v>
       </c>
       <c r="E150" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151">
-        <v>8234</v>
+        <v>8753</v>
       </c>
       <c r="B151" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C151">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D151">
-        <v>195.5</v>
+        <v>80.75</v>
       </c>
       <c r="E151" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152">
-        <v>8283</v>
+        <v>8754</v>
       </c>
       <c r="B152" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C152">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D152">
-        <v>735</v>
+        <v>80.75</v>
       </c>
       <c r="E152" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153">
-        <v>8283</v>
+        <v>8754</v>
       </c>
       <c r="B153" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C153">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D153">
-        <v>61.25</v>
+        <v>969</v>
       </c>
       <c r="E153" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154">
-        <v>8285</v>
+        <v>8756</v>
       </c>
       <c r="B154" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C154">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D154">
-        <v>61.25</v>
+        <v>969</v>
       </c>
       <c r="E154" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155">
-        <v>8285</v>
+        <v>8756</v>
       </c>
       <c r="B155" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C155">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D155">
-        <v>735</v>
+        <v>80.75</v>
       </c>
       <c r="E155" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156">
-        <v>8355</v>
+        <v>8923</v>
       </c>
       <c r="B156" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C156">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D156">
-        <v>326.75</v>
+        <v>339</v>
       </c>
       <c r="E156" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157">
-        <v>8660</v>
+        <v>8923</v>
       </c>
       <c r="B157" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C157">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D157">
-        <v>756.5</v>
+        <v>1017</v>
       </c>
       <c r="E157" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158">
-        <v>8968</v>
+        <v>8926</v>
       </c>
       <c r="B158" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C158">
         <v>1</v>
       </c>
       <c r="D158">
-        <v>756.5</v>
+        <v>482.25</v>
       </c>
       <c r="E158" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159">
-        <v>9081</v>
+        <v>8944</v>
       </c>
       <c r="B159" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C159">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D159">
-        <v>1452</v>
+        <v>131.25</v>
       </c>
       <c r="E159" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160">
-        <v>9081</v>
+        <v>8944</v>
       </c>
       <c r="B160" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C160">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D160">
-        <v>60.5</v>
+        <v>525</v>
       </c>
       <c r="E160" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161">
-        <v>9085</v>
+        <v>8968</v>
       </c>
       <c r="B161" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C161">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D161">
-        <v>315.5</v>
+        <v>756.5</v>
       </c>
       <c r="E161" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162">
-        <v>9085</v>
+        <v>9065</v>
       </c>
       <c r="B162" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="C162">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D162">
-        <v>946.5</v>
+        <v>736</v>
       </c>
       <c r="E162" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163">
-        <v>9087</v>
+        <v>9065</v>
       </c>
       <c r="B163" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C163">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D163">
-        <v>274.25</v>
+        <v>92</v>
       </c>
       <c r="E163" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164">
-        <v>9087</v>
+        <v>9068</v>
       </c>
       <c r="B164" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C164">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D164">
-        <v>822.75</v>
+        <v>236</v>
       </c>
       <c r="E164" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165">
-        <v>9088</v>
+        <v>9085</v>
       </c>
       <c r="B165" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="C165">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D165">
-        <v>816.75</v>
+        <v>315.5</v>
       </c>
       <c r="E165" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166">
-        <v>9088</v>
+        <v>9085</v>
       </c>
       <c r="B166" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="C166">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D166">
-        <v>272.25</v>
+        <v>946.5</v>
       </c>
       <c r="E166" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167">
-        <v>9129</v>
+        <v>9088</v>
       </c>
       <c r="B167" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C167">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D167">
-        <v>171.5</v>
+        <v>272.25</v>
       </c>
       <c r="E167" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168">
-        <v>9208</v>
+        <v>9088</v>
       </c>
       <c r="B168" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C168">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D168">
-        <v>303.25</v>
+        <v>816.75</v>
       </c>
       <c r="E168" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169">
-        <v>9208</v>
+        <v>9129</v>
       </c>
       <c r="B169" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="C169">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D169">
-        <v>909.75</v>
+        <v>171.5</v>
       </c>
       <c r="E169" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170">
-        <v>9209</v>
+        <v>9149</v>
       </c>
       <c r="B170" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C170">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D170">
-        <v>303.25</v>
+        <v>2490</v>
       </c>
       <c r="E170" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171">
-        <v>9209</v>
+        <v>9149</v>
       </c>
       <c r="B171" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C171">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D171">
-        <v>909.75</v>
+        <v>249</v>
       </c>
       <c r="E171" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172">
-        <v>9239</v>
+        <v>9149</v>
       </c>
       <c r="B172" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C172">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D172">
-        <v>1030.5</v>
+        <v>41.5</v>
       </c>
       <c r="E172" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173">
-        <v>9239</v>
+        <v>9621</v>
       </c>
       <c r="B173" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C173">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D173">
-        <v>343.5</v>
+        <v>24.75</v>
       </c>
       <c r="E173" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="174" spans="1:5">
       <c r="A174">
-        <v>9288</v>
+        <v>9621</v>
       </c>
       <c r="B174" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C174">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D174">
-        <v>458</v>
+        <v>297</v>
       </c>
       <c r="E174" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175">
-        <v>9507</v>
+        <v>9760</v>
       </c>
       <c r="B175" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C175">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D175">
-        <v>859.5</v>
+        <v>418.5</v>
       </c>
       <c r="E175" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176">
-        <v>9507</v>
+        <v>9784</v>
       </c>
       <c r="B176" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C176">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D176">
-        <v>143.25</v>
+        <v>403</v>
       </c>
       <c r="E176" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177">
-        <v>9621</v>
+        <v>10146</v>
       </c>
       <c r="B177" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C177">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D177">
-        <v>24.75</v>
+        <v>450.75</v>
       </c>
       <c r="E177" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="178" spans="1:5">
       <c r="A178">
-        <v>9621</v>
+        <v>10174</v>
       </c>
       <c r="B178" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C178">
         <v>1</v>
       </c>
       <c r="D178">
-        <v>297</v>
+        <v>747</v>
       </c>
       <c r="E178" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179">
-        <v>9760</v>
+        <v>10394</v>
       </c>
       <c r="B179" t="s">
+        <v>112</v>
+      </c>
+      <c r="C179">
+        <v>3</v>
+      </c>
+      <c r="D179">
         <v>104</v>
       </c>
-      <c r="C179">
-        <v>29</v>
-      </c>
-      <c r="D179">
-        <v>418.5</v>
-      </c>
       <c r="E179" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180">
-        <v>9820</v>
+        <v>10398</v>
       </c>
       <c r="B180" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C180">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D180">
-        <v>849</v>
+        <v>205.25</v>
       </c>
       <c r="E180" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181">
-        <v>9820</v>
+        <v>10446</v>
       </c>
       <c r="B181" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="C181">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D181">
-        <v>70.75</v>
+        <v>204</v>
       </c>
       <c r="E181" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182">
-        <v>10124</v>
+        <v>10446</v>
       </c>
       <c r="B182" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="C182">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D182">
-        <v>275.75</v>
+        <v>17</v>
       </c>
       <c r="E182" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="183" spans="1:5">
       <c r="A183">
-        <v>10172</v>
+        <v>10524</v>
       </c>
       <c r="B183" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="C183">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D183">
-        <v>240</v>
+        <v>719</v>
       </c>
       <c r="E183" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184">
-        <v>10172</v>
+        <v>10524</v>
       </c>
       <c r="B184" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="C184">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="D184">
-        <v>24</v>
+        <v>359.5</v>
       </c>
       <c r="E184" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="185" spans="1:5">
       <c r="A185">
-        <v>10394</v>
+        <v>10528</v>
       </c>
       <c r="B185" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C185">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D185">
-        <v>104</v>
+        <v>2112</v>
       </c>
       <c r="E185" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186">
-        <v>10524</v>
+        <v>10528</v>
       </c>
       <c r="B186" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C186">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D186">
-        <v>719</v>
+        <v>66</v>
       </c>
       <c r="E186" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="187" spans="1:5">
       <c r="A187">
-        <v>10524</v>
+        <v>10529</v>
       </c>
       <c r="B187" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C187">
         <v>80</v>
@@ -4204,41 +4231,41 @@
         <v>359.5</v>
       </c>
       <c r="E187" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="188" spans="1:5">
       <c r="A188">
-        <v>10527</v>
+        <v>10529</v>
       </c>
       <c r="B188" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C188">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D188">
-        <v>31.75</v>
+        <v>719</v>
       </c>
       <c r="E188" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="189" spans="1:5">
       <c r="A189">
-        <v>10527</v>
+        <v>10530</v>
       </c>
       <c r="B189" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="C189">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D189">
-        <v>1270</v>
+        <v>785.5</v>
       </c>
       <c r="E189" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -4246,7 +4273,7 @@
         <v>10530</v>
       </c>
       <c r="B190" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C190">
         <v>80</v>
@@ -4255,41 +4282,41 @@
         <v>392.75</v>
       </c>
       <c r="E190" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191">
-        <v>10530</v>
+        <v>10609</v>
       </c>
       <c r="B191" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="C191">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D191">
-        <v>785.5</v>
+        <v>98.75</v>
       </c>
       <c r="E191" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="192" spans="1:5">
       <c r="A192">
-        <v>10609</v>
+        <v>10640</v>
       </c>
       <c r="B192" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="C192">
         <v>1</v>
       </c>
       <c r="D192">
-        <v>98.75</v>
+        <v>187.5</v>
       </c>
       <c r="E192" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -4297,526 +4324,526 @@
         <v>10640</v>
       </c>
       <c r="B193" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C193">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D193">
-        <v>187.5</v>
+        <v>37.5</v>
       </c>
       <c r="E193" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="194" spans="1:5">
       <c r="A194">
-        <v>10640</v>
+        <v>10762</v>
       </c>
       <c r="B194" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="C194">
         <v>3</v>
       </c>
       <c r="D194">
-        <v>37.5</v>
+        <v>519.25</v>
       </c>
       <c r="E194" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="A195">
-        <v>10719</v>
+        <v>10762</v>
       </c>
       <c r="B195" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C195">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="D195">
-        <v>297</v>
+        <v>6231</v>
       </c>
       <c r="E195" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="196" spans="1:5">
       <c r="A196">
-        <v>10719</v>
+        <v>10830</v>
       </c>
       <c r="B196" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C196">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D196">
-        <v>891</v>
+        <v>427.25</v>
       </c>
       <c r="E196" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="197" spans="1:5">
       <c r="A197">
-        <v>10720</v>
+        <v>10830</v>
       </c>
       <c r="B197" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C197">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="D197">
-        <v>301.75</v>
+        <v>5127</v>
       </c>
       <c r="E197" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="198" spans="1:5">
       <c r="A198">
-        <v>10720</v>
+        <v>10897</v>
       </c>
       <c r="B198" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C198">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D198">
-        <v>905.25</v>
+        <v>85.25</v>
       </c>
       <c r="E198" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199">
-        <v>10721</v>
+        <v>11090</v>
       </c>
       <c r="B199" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="C199">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="D199">
-        <v>292.25</v>
+        <v>364</v>
       </c>
       <c r="E199" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200">
-        <v>10721</v>
+        <v>11091</v>
       </c>
       <c r="B200" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="C200">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D200">
-        <v>876.75</v>
+        <v>371</v>
       </c>
       <c r="E200" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201">
-        <v>10762</v>
+        <v>11092</v>
       </c>
       <c r="B201" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="C201">
         <v>1</v>
       </c>
       <c r="D201">
-        <v>6231</v>
+        <v>371</v>
       </c>
       <c r="E201" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="202" spans="1:5">
       <c r="A202">
-        <v>10762</v>
+        <v>11150</v>
       </c>
       <c r="B202" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="C202">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D202">
-        <v>519.25</v>
+        <v>84</v>
       </c>
       <c r="E202" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="203" spans="1:5">
       <c r="A203">
-        <v>10830</v>
+        <v>11150</v>
       </c>
       <c r="B203" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="C203">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D203">
-        <v>427.25</v>
+        <v>672</v>
       </c>
       <c r="E203" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="204" spans="1:5">
       <c r="A204">
-        <v>10830</v>
+        <v>11156</v>
       </c>
       <c r="B204" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="C204">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D204">
-        <v>5127</v>
+        <v>18</v>
       </c>
       <c r="E204" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="205" spans="1:5">
       <c r="A205">
-        <v>11092</v>
+        <v>11156</v>
       </c>
       <c r="B205" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="C205">
         <v>1</v>
       </c>
       <c r="D205">
-        <v>367</v>
+        <v>216</v>
       </c>
       <c r="E205" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="206" spans="1:5">
       <c r="A206">
-        <v>11150</v>
+        <v>11179</v>
       </c>
       <c r="B206" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="C206">
         <v>1</v>
       </c>
       <c r="D206">
-        <v>672</v>
+        <v>336</v>
       </c>
       <c r="E206" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="207" spans="1:5">
       <c r="A207">
-        <v>11150</v>
+        <v>11402</v>
       </c>
       <c r="B207" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="C207">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D207">
-        <v>84</v>
+        <v>674</v>
       </c>
       <c r="E207" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="208" spans="1:5">
       <c r="A208">
-        <v>11156</v>
+        <v>11411</v>
       </c>
       <c r="B208" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="C208">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D208">
-        <v>216</v>
+        <v>427</v>
       </c>
       <c r="E208" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="209" spans="1:5">
       <c r="A209">
-        <v>11156</v>
+        <v>11454</v>
       </c>
       <c r="B209" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="C209">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D209">
-        <v>18</v>
+        <v>74.75</v>
       </c>
       <c r="E209" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="210" spans="1:5">
       <c r="A210">
-        <v>11179</v>
+        <v>11504</v>
       </c>
       <c r="B210" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="C210">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D210">
-        <v>336</v>
+        <v>212.5</v>
       </c>
       <c r="E210" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="211" spans="1:5">
       <c r="A211">
-        <v>11411</v>
+        <v>11510</v>
       </c>
       <c r="B211" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="C211">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D211">
-        <v>427</v>
+        <v>50.75</v>
       </c>
       <c r="E211" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="212" spans="1:5">
       <c r="A212">
-        <v>11413</v>
+        <v>11510</v>
       </c>
       <c r="B212" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="C212">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D212">
-        <v>427.25</v>
+        <v>609</v>
       </c>
       <c r="E212" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="213" spans="1:5">
       <c r="A213">
-        <v>11510</v>
+        <v>11610</v>
       </c>
       <c r="B213" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="C213">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D213">
-        <v>609</v>
+        <v>187.5</v>
       </c>
       <c r="E213" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="214" spans="1:5">
       <c r="A214">
-        <v>11510</v>
+        <v>11610</v>
       </c>
       <c r="B214" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="C214">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D214">
-        <v>50.75</v>
+        <v>2250</v>
       </c>
       <c r="E214" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="215" spans="1:5">
       <c r="A215">
-        <v>11610</v>
+        <v>11625</v>
       </c>
       <c r="B215" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="C215">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D215">
-        <v>2250</v>
+        <v>323.75</v>
       </c>
       <c r="E215" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="216" spans="1:5">
       <c r="A216">
-        <v>11610</v>
+        <v>11633</v>
       </c>
       <c r="B216" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="C216">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D216">
-        <v>187.5</v>
+        <v>322.5</v>
       </c>
       <c r="E216" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="217" spans="1:5">
       <c r="A217">
-        <v>11625</v>
+        <v>11674</v>
       </c>
       <c r="B217" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="C217">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D217">
-        <v>323.75</v>
+        <v>145</v>
       </c>
       <c r="E217" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="218" spans="1:5">
       <c r="A218">
-        <v>11633</v>
+        <v>11687</v>
       </c>
       <c r="B218" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="C218">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D218">
-        <v>322.5</v>
+        <v>92</v>
       </c>
       <c r="E218" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="219" spans="1:5">
       <c r="A219">
-        <v>11677</v>
+        <v>11687</v>
       </c>
       <c r="B219" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="C219">
         <v>1</v>
       </c>
       <c r="D219">
-        <v>64</v>
+        <v>736</v>
       </c>
       <c r="E219" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="220" spans="1:5">
       <c r="A220">
-        <v>11685</v>
+        <v>11689</v>
       </c>
       <c r="B220" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="C220">
         <v>2</v>
       </c>
       <c r="D220">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="E220" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="221" spans="1:5">
       <c r="A221">
-        <v>11687</v>
+        <v>11689</v>
       </c>
       <c r="B221" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="C221">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D221">
-        <v>95</v>
+        <v>736</v>
       </c>
       <c r="E221" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="222" spans="1:5">
       <c r="A222">
-        <v>11687</v>
+        <v>11690</v>
       </c>
       <c r="B222" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="C222">
         <v>1</v>
       </c>
       <c r="D222">
-        <v>760</v>
+        <v>736</v>
       </c>
       <c r="E222" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="223" spans="1:5">
       <c r="A223">
-        <v>11710</v>
+        <v>11690</v>
       </c>
       <c r="B223" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="C223">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D223">
-        <v>31.75</v>
+        <v>92</v>
       </c>
       <c r="E223" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -4824,483 +4851,483 @@
         <v>11710</v>
       </c>
       <c r="B224" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="C224">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D224">
-        <v>222.25</v>
+        <v>31.75</v>
       </c>
       <c r="E224" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="225" spans="1:5">
       <c r="A225">
-        <v>11768</v>
+        <v>11710</v>
       </c>
       <c r="B225" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="C225">
         <v>1</v>
       </c>
       <c r="D225">
-        <v>182.75</v>
+        <v>222.25</v>
       </c>
       <c r="E225" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="226" spans="1:5">
       <c r="A226">
-        <v>11769</v>
+        <v>11768</v>
       </c>
       <c r="B226" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="C226">
         <v>1</v>
       </c>
       <c r="D226">
-        <v>183</v>
+        <v>182.75</v>
       </c>
       <c r="E226" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="227" spans="1:5">
       <c r="A227">
-        <v>11775</v>
+        <v>11769</v>
       </c>
       <c r="B227" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C227">
         <v>1</v>
       </c>
       <c r="D227">
-        <v>246</v>
+        <v>183</v>
       </c>
       <c r="E227" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="228" spans="1:5">
       <c r="A228">
-        <v>11836</v>
+        <v>11775</v>
       </c>
       <c r="B228" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C228">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D228">
-        <v>114</v>
+        <v>246</v>
       </c>
       <c r="E228" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="229" spans="1:5">
       <c r="A229">
-        <v>11844</v>
+        <v>11835</v>
       </c>
       <c r="B229" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="C229">
         <v>2</v>
       </c>
       <c r="D229">
-        <v>105.5</v>
+        <v>115.75</v>
       </c>
       <c r="E229" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="230" spans="1:5">
       <c r="A230">
-        <v>11887</v>
+        <v>11836</v>
       </c>
       <c r="B230" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C230">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D230">
-        <v>1210</v>
+        <v>114.25</v>
       </c>
       <c r="E230" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="231" spans="1:5">
       <c r="A231">
-        <v>11887</v>
+        <v>11838</v>
       </c>
       <c r="B231" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C231">
         <v>2</v>
       </c>
       <c r="D231">
-        <v>151.25</v>
+        <v>113.5</v>
       </c>
       <c r="E231" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="232" spans="1:5">
       <c r="A232">
-        <v>11909</v>
+        <v>11868</v>
       </c>
       <c r="B232" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="C232">
         <v>3</v>
       </c>
       <c r="D232">
-        <v>138.25</v>
+        <v>101</v>
       </c>
       <c r="E232" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="233" spans="1:5">
       <c r="A233">
-        <v>11909</v>
+        <v>11868</v>
       </c>
       <c r="B233" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="C233">
         <v>1</v>
       </c>
       <c r="D233">
-        <v>1659</v>
+        <v>808</v>
       </c>
       <c r="E233" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="234" spans="1:5">
       <c r="A234">
-        <v>11916</v>
+        <v>11885</v>
       </c>
       <c r="B234" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C234">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D234">
-        <v>102</v>
+        <v>1206</v>
       </c>
       <c r="E234" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="235" spans="1:5">
       <c r="A235">
-        <v>11916</v>
+        <v>11885</v>
       </c>
       <c r="B235" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C235">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D235">
-        <v>1224</v>
+        <v>150.75</v>
       </c>
       <c r="E235" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="236" spans="1:5">
       <c r="A236">
-        <v>12229</v>
+        <v>11886</v>
       </c>
       <c r="B236" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="C236">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D236">
-        <v>195.5</v>
+        <v>1206</v>
       </c>
       <c r="E236" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="237" spans="1:5">
       <c r="A237">
-        <v>12255</v>
+        <v>11886</v>
       </c>
       <c r="B237" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="C237">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D237">
-        <v>98.75</v>
+        <v>150.75</v>
       </c>
       <c r="E237" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="238" spans="1:5">
       <c r="A238">
-        <v>12255</v>
+        <v>11887</v>
       </c>
       <c r="B238" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="C238">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D238">
-        <v>395</v>
+        <v>150.75</v>
       </c>
       <c r="E238" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="239" spans="1:5">
       <c r="A239">
-        <v>12257</v>
+        <v>11887</v>
       </c>
       <c r="B239" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="C239">
         <v>1</v>
       </c>
       <c r="D239">
-        <v>397</v>
+        <v>1206</v>
       </c>
       <c r="E239" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="240" spans="1:5">
       <c r="A240">
-        <v>12257</v>
+        <v>11916</v>
       </c>
       <c r="B240" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="C240">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D240">
-        <v>99.25</v>
+        <v>102</v>
       </c>
       <c r="E240" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="241" spans="1:5">
       <c r="A241">
-        <v>12338</v>
+        <v>11916</v>
       </c>
       <c r="B241" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="C241">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D241">
-        <v>565</v>
+        <v>1224</v>
       </c>
       <c r="E241" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="242" spans="1:5">
       <c r="A242">
-        <v>12349</v>
+        <v>11942</v>
       </c>
       <c r="B242" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="C242">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D242">
-        <v>46.75</v>
+        <v>300</v>
       </c>
       <c r="E242" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="243" spans="1:5">
       <c r="A243">
-        <v>12352</v>
+        <v>11952</v>
       </c>
       <c r="B243" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="C243">
         <v>1</v>
       </c>
       <c r="D243">
-        <v>48</v>
+        <v>147.75</v>
       </c>
       <c r="E243" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="244" spans="1:5">
       <c r="A244">
-        <v>12498</v>
+        <v>12255</v>
       </c>
       <c r="B244" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="C244">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D244">
-        <v>60.25</v>
+        <v>98.75</v>
       </c>
       <c r="E244" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="245" spans="1:5">
       <c r="A245">
-        <v>12498</v>
+        <v>12255</v>
       </c>
       <c r="B245" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="C245">
         <v>1</v>
       </c>
       <c r="D245">
-        <v>602.5</v>
+        <v>395</v>
       </c>
       <c r="E245" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="246" spans="1:5">
       <c r="A246">
-        <v>12576</v>
+        <v>12257</v>
       </c>
       <c r="B246" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="C246">
         <v>1</v>
       </c>
       <c r="D246">
-        <v>618</v>
+        <v>397</v>
       </c>
       <c r="E246" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="247" spans="1:5">
       <c r="A247">
-        <v>12576</v>
+        <v>12257</v>
       </c>
       <c r="B247" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="C247">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D247">
-        <v>51.5</v>
+        <v>99.25</v>
       </c>
       <c r="E247" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="248" spans="1:5">
       <c r="A248">
-        <v>12577</v>
+        <v>12338</v>
       </c>
       <c r="B248" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="C248">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D248">
-        <v>618</v>
+        <v>565</v>
       </c>
       <c r="E248" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="249" spans="1:5">
       <c r="A249">
-        <v>12577</v>
+        <v>12349</v>
       </c>
       <c r="B249" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="C249">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D249">
-        <v>51.5</v>
+        <v>46.25</v>
       </c>
       <c r="E249" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="250" spans="1:5">
       <c r="A250">
-        <v>12587</v>
+        <v>12498</v>
       </c>
       <c r="B250" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="C250">
         <v>1</v>
       </c>
       <c r="D250">
-        <v>618</v>
+        <v>602.5</v>
       </c>
       <c r="E250" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="251" spans="1:5">
       <c r="A251">
-        <v>12587</v>
+        <v>12498</v>
       </c>
       <c r="B251" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="C251">
         <v>3</v>
       </c>
       <c r="D251">
-        <v>51.5</v>
+        <v>60.25</v>
       </c>
       <c r="E251" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="252" spans="1:5">
       <c r="A252">
-        <v>12588</v>
+        <v>12576</v>
       </c>
       <c r="B252" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="C252">
         <v>3</v>
@@ -5309,15 +5336,15 @@
         <v>51.5</v>
       </c>
       <c r="E252" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="253" spans="1:5">
       <c r="A253">
-        <v>12588</v>
+        <v>12576</v>
       </c>
       <c r="B253" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -5326,1486 +5353,1503 @@
         <v>618</v>
       </c>
       <c r="E253" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="254" spans="1:5">
       <c r="A254">
-        <v>12637</v>
+        <v>12577</v>
       </c>
       <c r="B254" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="C254">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D254">
-        <v>88.75</v>
+        <v>51.5</v>
       </c>
       <c r="E254" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="255" spans="1:5">
       <c r="A255">
-        <v>12648</v>
+        <v>12577</v>
       </c>
       <c r="B255" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="C255">
         <v>1</v>
       </c>
       <c r="D255">
-        <v>208.25</v>
+        <v>618</v>
       </c>
       <c r="E255" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="256" spans="1:5">
       <c r="A256">
-        <v>12952</v>
+        <v>12585</v>
       </c>
       <c r="B256" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="C256">
         <v>1</v>
       </c>
       <c r="D256">
-        <v>534</v>
+        <v>606</v>
       </c>
       <c r="E256" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="257" spans="1:5">
       <c r="A257">
-        <v>12952</v>
+        <v>12585</v>
       </c>
       <c r="B257" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="C257">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D257">
-        <v>133.5</v>
+        <v>50.5</v>
       </c>
       <c r="E257" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="258" spans="1:5">
       <c r="A258">
-        <v>12980</v>
+        <v>12587</v>
       </c>
       <c r="B258" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="C258">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D258">
-        <v>716</v>
+        <v>51.5</v>
       </c>
       <c r="E258" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="259" spans="1:5">
       <c r="A259">
-        <v>12980</v>
+        <v>12587</v>
       </c>
       <c r="B259" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="C259">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D259">
-        <v>44.75</v>
+        <v>618</v>
       </c>
       <c r="E259" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="260" spans="1:5">
       <c r="A260">
-        <v>12993</v>
+        <v>12588</v>
       </c>
       <c r="B260" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="C260">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D260">
-        <v>14</v>
+        <v>618</v>
       </c>
       <c r="E260" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="261" spans="1:5">
       <c r="A261">
-        <v>12993</v>
+        <v>12588</v>
       </c>
       <c r="B261" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="C261">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D261">
-        <v>280</v>
+        <v>51.5</v>
       </c>
       <c r="E261" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="262" spans="1:5">
       <c r="A262">
-        <v>13244</v>
+        <v>12676</v>
       </c>
       <c r="B262" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="C262">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D262">
-        <v>580</v>
+        <v>271.5</v>
       </c>
       <c r="E262" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="263" spans="1:5">
       <c r="A263">
-        <v>13244</v>
+        <v>12676</v>
       </c>
       <c r="B263" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="C263">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D263">
-        <v>72.5</v>
+        <v>1357.5</v>
       </c>
       <c r="E263" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="264" spans="1:5">
       <c r="A264">
-        <v>13247</v>
+        <v>12676</v>
       </c>
       <c r="B264" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C264">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D264">
-        <v>331.25</v>
+        <v>6787.5</v>
       </c>
       <c r="E264" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="265" spans="1:5">
       <c r="A265">
-        <v>13252</v>
+        <v>12924</v>
       </c>
       <c r="B265" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="C265">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D265">
-        <v>269</v>
+        <v>564</v>
       </c>
       <c r="E265" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="266" spans="1:5">
       <c r="A266">
-        <v>13257</v>
+        <v>13028</v>
       </c>
       <c r="B266" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="C266">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D266">
-        <v>375.25</v>
+        <v>200</v>
       </c>
       <c r="E266" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="267" spans="1:5">
       <c r="A267">
-        <v>13257</v>
+        <v>13247</v>
       </c>
       <c r="B267" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="C267">
         <v>29</v>
       </c>
       <c r="D267">
-        <v>750.5</v>
+        <v>332.25</v>
       </c>
       <c r="E267" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="268" spans="1:5">
       <c r="A268">
-        <v>13258</v>
+        <v>13253</v>
       </c>
       <c r="B268" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="C268">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D268">
-        <v>371.5</v>
+        <v>274.75</v>
       </c>
       <c r="E268" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="269" spans="1:5">
       <c r="A269">
-        <v>13258</v>
+        <v>13264</v>
       </c>
       <c r="B269" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="C269">
         <v>29</v>
       </c>
       <c r="D269">
-        <v>743</v>
+        <v>410.5</v>
       </c>
       <c r="E269" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="270" spans="1:5">
       <c r="A270">
-        <v>13259</v>
+        <v>13276</v>
       </c>
       <c r="B270" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="C270">
         <v>29</v>
       </c>
       <c r="D270">
-        <v>834</v>
+        <v>364.25</v>
       </c>
       <c r="E270" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="271" spans="1:5">
       <c r="A271">
-        <v>13259</v>
+        <v>13486</v>
       </c>
       <c r="B271" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C271">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D271">
-        <v>417</v>
+        <v>235</v>
       </c>
       <c r="E271" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="272" spans="1:5">
       <c r="A272">
-        <v>13260</v>
+        <v>13599</v>
       </c>
       <c r="B272" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="C272">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D272">
-        <v>411.5</v>
+        <v>93</v>
       </c>
       <c r="E272" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="273" spans="1:5">
       <c r="A273">
-        <v>13269</v>
+        <v>13604</v>
       </c>
       <c r="B273" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="C273">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D273">
-        <v>390.75</v>
+        <v>284.25</v>
       </c>
       <c r="E273" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="274" spans="1:5">
       <c r="A274">
-        <v>13272</v>
+        <v>13606</v>
       </c>
       <c r="B274" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="C274">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D274">
-        <v>292.75</v>
+        <v>366</v>
       </c>
       <c r="E274" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="275" spans="1:5">
       <c r="A275">
-        <v>13276</v>
+        <v>13608</v>
       </c>
       <c r="B275" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="C275">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D275">
-        <v>376.5</v>
+        <v>581.25</v>
       </c>
       <c r="E275" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="276" spans="1:5">
       <c r="A276">
-        <v>13329</v>
+        <v>13928</v>
       </c>
       <c r="B276" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="C276">
         <v>2</v>
       </c>
       <c r="D276">
-        <v>317.5</v>
+        <v>1217.5</v>
       </c>
       <c r="E276" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="277" spans="1:5">
       <c r="A277">
-        <v>13330</v>
+        <v>13928</v>
       </c>
       <c r="B277" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="C277">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D277">
-        <v>316</v>
+        <v>608.75</v>
       </c>
       <c r="E277" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="278" spans="1:5">
       <c r="A278">
-        <v>13599</v>
+        <v>13964</v>
       </c>
       <c r="B278" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="C278">
         <v>1</v>
       </c>
       <c r="D278">
-        <v>93</v>
+        <v>284.5</v>
       </c>
       <c r="E278" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="279" spans="1:5">
       <c r="A279">
-        <v>13604</v>
+        <v>13966</v>
       </c>
       <c r="B279" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="C279">
         <v>1</v>
       </c>
       <c r="D279">
-        <v>284.25</v>
+        <v>295</v>
       </c>
       <c r="E279" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="280" spans="1:5">
       <c r="A280">
-        <v>13606</v>
+        <v>13968</v>
       </c>
       <c r="B280" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="C280">
         <v>1</v>
       </c>
       <c r="D280">
-        <v>366</v>
+        <v>285</v>
       </c>
       <c r="E280" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="281" spans="1:5">
       <c r="A281">
-        <v>13608</v>
+        <v>18964</v>
       </c>
       <c r="B281" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="C281">
         <v>1</v>
       </c>
       <c r="D281">
-        <v>581.25</v>
+        <v>443.25</v>
       </c>
       <c r="E281" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="282" spans="1:5">
       <c r="A282">
-        <v>13928</v>
+        <v>19686</v>
       </c>
       <c r="B282" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="C282">
         <v>1</v>
       </c>
       <c r="D282">
-        <v>612.5</v>
+        <v>953.75</v>
       </c>
       <c r="E282" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="283" spans="1:5">
       <c r="A283">
-        <v>13928</v>
+        <v>19980</v>
       </c>
       <c r="B283" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="C283">
         <v>2</v>
       </c>
       <c r="D283">
-        <v>1225</v>
+        <v>519.25</v>
       </c>
       <c r="E283" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="284" spans="1:5">
       <c r="A284">
-        <v>13967</v>
+        <v>19986</v>
       </c>
       <c r="B284" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="C284">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D284">
-        <v>298.5</v>
+        <v>506.5</v>
       </c>
       <c r="E284" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="285" spans="1:5">
       <c r="A285">
-        <v>18964</v>
+        <v>20555</v>
       </c>
       <c r="B285" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C285">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D285">
-        <v>443.25</v>
+        <v>488</v>
       </c>
       <c r="E285" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="286" spans="1:5">
       <c r="A286">
-        <v>19983</v>
+        <v>20650</v>
       </c>
       <c r="B286" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="C286">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D286">
-        <v>451.5</v>
+        <v>237</v>
       </c>
       <c r="E286" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="287" spans="1:5">
       <c r="A287">
-        <v>19985</v>
+        <v>21081</v>
       </c>
       <c r="B287" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="C287">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D287">
-        <v>451.5</v>
+        <v>86</v>
       </c>
       <c r="E287" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="288" spans="1:5">
       <c r="A288">
-        <v>19986</v>
+        <v>21081</v>
       </c>
       <c r="B288" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="C288">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D288">
-        <v>508.5</v>
+        <v>1548</v>
       </c>
       <c r="E288" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="289" spans="1:5">
       <c r="A289">
-        <v>19987</v>
+        <v>21703</v>
       </c>
       <c r="B289" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="C289">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D289">
-        <v>451.5</v>
+        <v>1152</v>
       </c>
       <c r="E289" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="290" spans="1:5">
       <c r="A290">
-        <v>19988</v>
+        <v>21703</v>
       </c>
       <c r="B290" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="C290">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D290">
-        <v>508.5</v>
+        <v>96</v>
       </c>
       <c r="E290" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="291" spans="1:5">
       <c r="A291">
-        <v>19989</v>
+        <v>21705</v>
       </c>
       <c r="B291" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="C291">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D291">
-        <v>451.5</v>
+        <v>870</v>
       </c>
       <c r="E291" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="292" spans="1:5">
       <c r="A292">
-        <v>19991</v>
+        <v>21705</v>
       </c>
       <c r="B292" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C292">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D292">
-        <v>451.5</v>
+        <v>36.25</v>
       </c>
       <c r="E292" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="293" spans="1:5">
       <c r="A293">
-        <v>19996</v>
+        <v>21707</v>
       </c>
       <c r="B293" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C293">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D293">
-        <v>508.5</v>
+        <v>53</v>
       </c>
       <c r="E293" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="294" spans="1:5">
       <c r="A294">
-        <v>19997</v>
+        <v>21707</v>
       </c>
       <c r="B294" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C294">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D294">
-        <v>451.5</v>
+        <v>1272</v>
       </c>
       <c r="E294" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="295" spans="1:5">
       <c r="A295">
-        <v>20555</v>
+        <v>21709</v>
       </c>
       <c r="B295" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="C295">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D295">
-        <v>491.75</v>
+        <v>37.75</v>
       </c>
       <c r="E295" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="296" spans="1:5">
       <c r="A296">
-        <v>20682</v>
+        <v>21709</v>
       </c>
       <c r="B296" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C296">
         <v>1</v>
       </c>
       <c r="D296">
-        <v>45.5</v>
+        <v>1132.5</v>
       </c>
       <c r="E296" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="297" spans="1:5">
       <c r="A297">
-        <v>21793</v>
+        <v>21745</v>
       </c>
       <c r="B297" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C297">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D297">
-        <v>122</v>
+        <v>417.5</v>
       </c>
       <c r="E297" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="298" spans="1:5">
       <c r="A298">
-        <v>21810</v>
+        <v>21752</v>
       </c>
       <c r="B298" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C298">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D298">
-        <v>314.75</v>
+        <v>474.25</v>
       </c>
       <c r="E298" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="299" spans="1:5">
       <c r="A299">
-        <v>22318</v>
+        <v>21754</v>
       </c>
       <c r="B299" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="C299">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D299">
-        <v>794</v>
+        <v>417.5</v>
       </c>
       <c r="E299" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="300" spans="1:5">
       <c r="A300">
-        <v>22318</v>
+        <v>21771</v>
       </c>
       <c r="B300" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C300">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D300">
-        <v>99.25</v>
+        <v>417.5</v>
       </c>
       <c r="E300" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="301" spans="1:5">
       <c r="A301">
-        <v>22361</v>
+        <v>21773</v>
       </c>
       <c r="B301" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="C301">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D301">
-        <v>694.25</v>
+        <v>368.5</v>
       </c>
       <c r="E301" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="302" spans="1:5">
       <c r="A302">
-        <v>22587</v>
+        <v>21777</v>
       </c>
       <c r="B302" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C302">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D302">
-        <v>54</v>
+        <v>368.5</v>
       </c>
       <c r="E302" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="303" spans="1:5">
       <c r="A303">
-        <v>22587</v>
+        <v>21789</v>
       </c>
       <c r="B303" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="C303">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D303">
-        <v>648</v>
+        <v>310</v>
       </c>
       <c r="E303" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="304" spans="1:5">
       <c r="A304">
-        <v>22708</v>
+        <v>21810</v>
       </c>
       <c r="B304" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="C304">
         <v>1</v>
       </c>
       <c r="D304">
-        <v>355</v>
+        <v>310.5</v>
       </c>
       <c r="E304" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="305" spans="1:5">
       <c r="A305">
-        <v>23235</v>
+        <v>21820</v>
       </c>
       <c r="B305" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="C305">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D305">
-        <v>354.5</v>
+        <v>184.25</v>
       </c>
       <c r="E305" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="306" spans="1:5">
       <c r="A306">
-        <v>23235</v>
+        <v>21820</v>
       </c>
       <c r="B306" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="C306">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D306">
-        <v>1063.5</v>
+        <v>737</v>
       </c>
       <c r="E306" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="307" spans="1:5">
       <c r="A307">
-        <v>23237</v>
+        <v>22126</v>
       </c>
       <c r="B307" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="C307">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D307">
-        <v>407.5</v>
+        <v>368.5</v>
       </c>
       <c r="E307" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="308" spans="1:5">
       <c r="A308">
-        <v>23237</v>
+        <v>22587</v>
       </c>
       <c r="B308" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="C308">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D308">
-        <v>815</v>
+        <v>55</v>
       </c>
       <c r="E308" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="309" spans="1:5">
       <c r="A309">
-        <v>23238</v>
+        <v>22587</v>
       </c>
       <c r="B309" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="C309">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D309">
-        <v>410.25</v>
+        <v>660</v>
       </c>
       <c r="E309" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="310" spans="1:5">
       <c r="A310">
-        <v>23238</v>
+        <v>23040</v>
       </c>
       <c r="B310" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="C310">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D310">
-        <v>820.5</v>
+        <v>318</v>
       </c>
       <c r="E310" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="311" spans="1:5">
       <c r="A311">
-        <v>23248</v>
+        <v>23040</v>
       </c>
       <c r="B311" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="C311">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="D311">
-        <v>673</v>
+        <v>26.5</v>
       </c>
       <c r="E311" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="312" spans="1:5">
       <c r="A312">
-        <v>23248</v>
+        <v>23237</v>
       </c>
       <c r="B312" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="C312">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D312">
-        <v>336.5</v>
+        <v>815</v>
       </c>
       <c r="E312" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="313" spans="1:5">
       <c r="A313">
-        <v>23382</v>
+        <v>23237</v>
       </c>
       <c r="B313" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="C313">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D313">
-        <v>588</v>
+        <v>407.5</v>
       </c>
       <c r="E313" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="314" spans="1:5">
       <c r="A314">
-        <v>23382</v>
+        <v>23239</v>
       </c>
       <c r="B314" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="C314">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D314">
-        <v>49</v>
+        <v>397</v>
       </c>
       <c r="E314" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="315" spans="1:5">
       <c r="A315">
-        <v>23534</v>
+        <v>23239</v>
       </c>
       <c r="B315" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="C315">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D315">
-        <v>594</v>
+        <v>794</v>
       </c>
       <c r="E315" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="316" spans="1:5">
       <c r="A316">
-        <v>23534</v>
+        <v>23248</v>
       </c>
       <c r="B316" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="C316">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D316">
-        <v>49.5</v>
+        <v>336.5</v>
       </c>
       <c r="E316" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="317" spans="1:5">
       <c r="A317">
-        <v>23537</v>
+        <v>23248</v>
       </c>
       <c r="B317" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="C317">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D317">
-        <v>24.75</v>
+        <v>673</v>
       </c>
       <c r="E317" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="318" spans="1:5">
       <c r="A318">
-        <v>23537</v>
+        <v>23261</v>
       </c>
       <c r="B318" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="C318">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D318">
-        <v>297</v>
+        <v>99.25</v>
       </c>
       <c r="E318" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="319" spans="1:5">
       <c r="A319">
-        <v>23538</v>
+        <v>23380</v>
       </c>
       <c r="B319" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="C319">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D319">
-        <v>38.25</v>
+        <v>919.5</v>
       </c>
       <c r="E319" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="320" spans="1:5">
       <c r="A320">
-        <v>23538</v>
+        <v>23380</v>
       </c>
       <c r="B320" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="C320">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D320">
-        <v>459</v>
+        <v>306.5</v>
       </c>
       <c r="E320" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="321" spans="1:5">
       <c r="A321">
-        <v>23546</v>
+        <v>23382</v>
       </c>
       <c r="B321" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C321">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D321">
-        <v>47</v>
+        <v>588</v>
       </c>
       <c r="E321" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="322" spans="1:5">
       <c r="A322">
-        <v>23546</v>
+        <v>23382</v>
       </c>
       <c r="B322" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C322">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D322">
-        <v>564</v>
+        <v>49</v>
       </c>
       <c r="E322" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="323" spans="1:5">
       <c r="A323">
-        <v>23601</v>
+        <v>23492</v>
       </c>
       <c r="B323" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C323">
         <v>1</v>
       </c>
       <c r="D323">
-        <v>633</v>
+        <v>2780</v>
       </c>
       <c r="E323" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="324" spans="1:5">
       <c r="A324">
-        <v>23601</v>
+        <v>23492</v>
       </c>
       <c r="B324" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C324">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D324">
-        <v>52.75</v>
+        <v>139</v>
       </c>
       <c r="E324" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="325" spans="1:5">
       <c r="A325">
-        <v>23662</v>
+        <v>23534</v>
       </c>
       <c r="B325" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="C325">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D325">
-        <v>279</v>
+        <v>594</v>
       </c>
       <c r="E325" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="326" spans="1:5">
       <c r="A326">
-        <v>23992</v>
+        <v>23534</v>
       </c>
       <c r="B326" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="C326">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D326">
-        <v>359.5</v>
+        <v>49.5</v>
       </c>
       <c r="E326" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="327" spans="1:5">
       <c r="A327">
-        <v>23992</v>
+        <v>23537</v>
       </c>
       <c r="B327" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="C327">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D327">
-        <v>719</v>
+        <v>297</v>
       </c>
       <c r="E327" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="328" spans="1:5">
       <c r="A328">
-        <v>23994</v>
+        <v>23537</v>
       </c>
       <c r="B328" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="C328">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D328">
-        <v>392.75</v>
+        <v>24.75</v>
       </c>
       <c r="E328" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="329" spans="1:5">
       <c r="A329">
-        <v>23994</v>
+        <v>23598</v>
       </c>
       <c r="B329" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="C329">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D329">
-        <v>785.5</v>
+        <v>786</v>
       </c>
       <c r="E329" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="330" spans="1:5">
       <c r="A330">
-        <v>24257</v>
+        <v>23598</v>
       </c>
       <c r="B330" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="C330">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D330">
-        <v>209</v>
+        <v>131</v>
       </c>
       <c r="E330" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="331" spans="1:5">
       <c r="A331">
-        <v>24258</v>
+        <v>23601</v>
       </c>
       <c r="B331" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="C331">
         <v>1</v>
       </c>
       <c r="D331">
-        <v>207.5</v>
+        <v>633</v>
       </c>
       <c r="E331" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="332" spans="1:5">
       <c r="A332">
-        <v>24705</v>
+        <v>23601</v>
       </c>
       <c r="B332" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="C332">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D332">
-        <v>156</v>
+        <v>52.75</v>
       </c>
       <c r="E332" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="333" spans="1:5">
       <c r="A333">
-        <v>24844</v>
+        <v>23661</v>
       </c>
       <c r="B333" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C333">
         <v>2</v>
       </c>
       <c r="D333">
-        <v>161.75</v>
+        <v>279.5</v>
       </c>
       <c r="E333" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="334" spans="1:5">
       <c r="A334">
-        <v>25958</v>
+        <v>23994</v>
       </c>
       <c r="B334" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="C334">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D334">
-        <v>108</v>
+        <v>392.75</v>
       </c>
       <c r="E334" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="335" spans="1:5">
       <c r="A335">
-        <v>26125</v>
+        <v>23994</v>
       </c>
       <c r="B335" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="C335">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="D335">
-        <v>64.5</v>
+        <v>785.5</v>
       </c>
       <c r="E335" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="336" spans="1:5">
       <c r="A336">
-        <v>26125</v>
+        <v>24670</v>
       </c>
       <c r="B336" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="C336">
         <v>1</v>
       </c>
       <c r="D336">
-        <v>774</v>
+        <v>945.25</v>
       </c>
       <c r="E336" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="337" spans="1:5">
       <c r="A337">
-        <v>26127</v>
+        <v>24705</v>
       </c>
       <c r="B337" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C337">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D337">
-        <v>514</v>
+        <v>152</v>
       </c>
       <c r="E337" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="338" spans="1:5">
       <c r="A338">
-        <v>26127</v>
+        <v>24844</v>
       </c>
       <c r="B338" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C338">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D338">
-        <v>64.25</v>
+        <v>152</v>
       </c>
       <c r="E338" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="339" spans="1:5">
       <c r="A339">
-        <v>26128</v>
+        <v>24889</v>
       </c>
       <c r="B339" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C339">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D339">
-        <v>64.75</v>
+        <v>151.5</v>
       </c>
       <c r="E339" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="340" spans="1:5">
       <c r="A340">
-        <v>26128</v>
+        <v>25344</v>
       </c>
       <c r="B340" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="C340">
         <v>1</v>
       </c>
       <c r="D340">
-        <v>518</v>
+        <v>2847</v>
       </c>
       <c r="E340" t="s">
-        <v>214</v>
+        <v>223</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5">
+      <c r="A341">
+        <v>25344</v>
+      </c>
+      <c r="B341" t="s">
+        <v>222</v>
+      </c>
+      <c r="C341">
+        <v>3</v>
+      </c>
+      <c r="D341">
+        <v>237.25</v>
+      </c>
+      <c r="E341" t="s">
+        <v>223</v>
       </c>
     </row>
   </sheetData>
